--- a/LF/improvements_aayush/results/Step5_BERT_Results_1.xlsx
+++ b/LF/improvements_aayush/results/Step5_BERT_Results_1.xlsx
@@ -9793,19 +9793,19 @@
         <v>583</v>
       </c>
       <c r="F2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2">
-        <v>0.08400000000000001</v>
+        <v>0.1969999969005585</v>
       </c>
       <c r="I2">
-        <v>0.534</v>
+        <v>0.2720000147819519</v>
       </c>
       <c r="J2">
-        <v>0.383</v>
+        <v>0.5320000052452087</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -9825,19 +9825,19 @@
         <v>584</v>
       </c>
       <c r="F3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H3">
-        <v>0.171</v>
+        <v>0.1389999985694885</v>
       </c>
       <c r="I3">
-        <v>0.16</v>
+        <v>0.4729999899864197</v>
       </c>
       <c r="J3">
-        <v>0.669</v>
+        <v>0.3880000114440918</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -9857,19 +9857,19 @@
         <v>583</v>
       </c>
       <c r="F4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H4">
-        <v>0.057</v>
+        <v>0.1430000066757202</v>
       </c>
       <c r="I4">
-        <v>0.659</v>
+        <v>0.2660000026226044</v>
       </c>
       <c r="J4">
-        <v>0.284</v>
+        <v>0.5920000076293945</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -9895,13 +9895,13 @@
         <v>583</v>
       </c>
       <c r="H5">
-        <v>0.166</v>
+        <v>0.07199999690055847</v>
       </c>
       <c r="I5">
-        <v>0.395</v>
+        <v>0.3919999897480011</v>
       </c>
       <c r="J5">
-        <v>0.439</v>
+        <v>0.5360000133514404</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -9927,13 +9927,13 @@
         <v>583</v>
       </c>
       <c r="H6">
-        <v>0.108</v>
+        <v>0.1379999965429306</v>
       </c>
       <c r="I6">
-        <v>0.516</v>
+        <v>0.6150000095367432</v>
       </c>
       <c r="J6">
-        <v>0.376</v>
+        <v>0.2469999939203262</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -9959,13 +9959,13 @@
         <v>583</v>
       </c>
       <c r="H7">
-        <v>0.135</v>
+        <v>0.07900000363588333</v>
       </c>
       <c r="I7">
-        <v>0.619</v>
+        <v>0.4620000123977661</v>
       </c>
       <c r="J7">
-        <v>0.245</v>
+        <v>0.4600000083446503</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -9991,13 +9991,13 @@
         <v>584</v>
       </c>
       <c r="H8">
-        <v>0.08500000000000001</v>
+        <v>0.221000000834465</v>
       </c>
       <c r="I8">
-        <v>0.673</v>
+        <v>0.4519999921321869</v>
       </c>
       <c r="J8">
-        <v>0.242</v>
+        <v>0.3269999921321869</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -10017,19 +10017,19 @@
         <v>584</v>
       </c>
       <c r="F9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H9">
-        <v>0.092</v>
+        <v>0.1909999996423721</v>
       </c>
       <c r="I9">
-        <v>0.263</v>
+        <v>0.4059999883174896</v>
       </c>
       <c r="J9">
-        <v>0.646</v>
+        <v>0.4040000140666962</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -10049,19 +10049,19 @@
         <v>583</v>
       </c>
       <c r="F10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G10" t="s">
         <v>584</v>
       </c>
       <c r="H10">
-        <v>0.33</v>
+        <v>0.09600000083446503</v>
       </c>
       <c r="I10">
-        <v>0.33</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="J10">
-        <v>0.34</v>
+        <v>0.4350000023841858</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -10087,13 +10087,13 @@
         <v>583</v>
       </c>
       <c r="H11">
-        <v>0.129</v>
+        <v>0.1049999967217445</v>
       </c>
       <c r="I11">
-        <v>0.58</v>
+        <v>0.5130000114440918</v>
       </c>
       <c r="J11">
-        <v>0.291</v>
+        <v>0.3819999992847443</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -10113,19 +10113,19 @@
         <v>583</v>
       </c>
       <c r="F12" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G12" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H12">
-        <v>0.093</v>
+        <v>0.1439999938011169</v>
       </c>
       <c r="I12">
-        <v>0.549</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="J12">
-        <v>0.358</v>
+        <v>0.5759999752044678</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -10151,13 +10151,13 @@
         <v>583</v>
       </c>
       <c r="H13">
-        <v>0.261</v>
+        <v>0.1099999994039536</v>
       </c>
       <c r="I13">
-        <v>0.388</v>
+        <v>0.5379999876022339</v>
       </c>
       <c r="J13">
-        <v>0.351</v>
+        <v>0.3519999980926514</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -10177,19 +10177,19 @@
         <v>584</v>
       </c>
       <c r="F14" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G14" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H14">
-        <v>0.33</v>
+        <v>0.1400000005960464</v>
       </c>
       <c r="I14">
-        <v>0.33</v>
+        <v>0.6010000109672546</v>
       </c>
       <c r="J14">
-        <v>0.34</v>
+        <v>0.2590000033378601</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -10209,19 +10209,19 @@
         <v>583</v>
       </c>
       <c r="F15" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G15" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H15">
-        <v>0.33</v>
+        <v>0.1340000033378601</v>
       </c>
       <c r="I15">
-        <v>0.33</v>
+        <v>0.2169999927282333</v>
       </c>
       <c r="J15">
-        <v>0.34</v>
+        <v>0.6499999761581421</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -10241,19 +10241,19 @@
         <v>584</v>
       </c>
       <c r="F16" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G16" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H16">
-        <v>0.33</v>
+        <v>0.1739999949932098</v>
       </c>
       <c r="I16">
-        <v>0.33</v>
+        <v>0.5809999704360962</v>
       </c>
       <c r="J16">
-        <v>0.34</v>
+        <v>0.2450000047683716</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -10279,13 +10279,13 @@
         <v>584</v>
       </c>
       <c r="H17">
-        <v>0.133</v>
+        <v>0.1369999945163727</v>
       </c>
       <c r="I17">
-        <v>0.478</v>
+        <v>0.5889999866485596</v>
       </c>
       <c r="J17">
-        <v>0.389</v>
+        <v>0.2739999890327454</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -10305,19 +10305,19 @@
         <v>583</v>
       </c>
       <c r="F18" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G18" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H18">
-        <v>0.33</v>
+        <v>0.09000000357627869</v>
       </c>
       <c r="I18">
-        <v>0.33</v>
+        <v>0.4350000023841858</v>
       </c>
       <c r="J18">
-        <v>0.34</v>
+        <v>0.4740000069141388</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -10337,19 +10337,19 @@
         <v>583</v>
       </c>
       <c r="F19" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H19">
-        <v>0.33</v>
+        <v>0.09099999815225601</v>
       </c>
       <c r="I19">
-        <v>0.33</v>
+        <v>0.2649999856948853</v>
       </c>
       <c r="J19">
-        <v>0.34</v>
+        <v>0.6439999938011169</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -10369,19 +10369,19 @@
         <v>583</v>
       </c>
       <c r="F20" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G20" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H20">
-        <v>0.33</v>
+        <v>0.07699999958276749</v>
       </c>
       <c r="I20">
-        <v>0.33</v>
+        <v>0.460999995470047</v>
       </c>
       <c r="J20">
-        <v>0.34</v>
+        <v>0.4620000123977661</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -10401,19 +10401,19 @@
         <v>584</v>
       </c>
       <c r="F21" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G21" t="s">
         <v>584</v>
       </c>
       <c r="H21">
-        <v>0.325</v>
+        <v>0.1220000013709068</v>
       </c>
       <c r="I21">
-        <v>0.26</v>
+        <v>0.5519999861717224</v>
       </c>
       <c r="J21">
-        <v>0.414</v>
+        <v>0.3260000050067902</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -10433,19 +10433,19 @@
         <v>584</v>
       </c>
       <c r="F22" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G22" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H22">
-        <v>0.33</v>
+        <v>0.2660000026226044</v>
       </c>
       <c r="I22">
-        <v>0.33</v>
+        <v>0.2930000126361847</v>
       </c>
       <c r="J22">
-        <v>0.34</v>
+        <v>0.4420000016689301</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -10465,19 +10465,19 @@
         <v>583</v>
       </c>
       <c r="F23" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G23" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H23">
-        <v>0.33</v>
+        <v>0.135000005364418</v>
       </c>
       <c r="I23">
-        <v>0.33</v>
+        <v>0.6150000095367432</v>
       </c>
       <c r="J23">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -10497,19 +10497,19 @@
         <v>583</v>
       </c>
       <c r="F24" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G24" t="s">
         <v>584</v>
       </c>
       <c r="H24">
-        <v>0.33</v>
+        <v>0.08100000023841858</v>
       </c>
       <c r="I24">
-        <v>0.33</v>
+        <v>0.5339999794960022</v>
       </c>
       <c r="J24">
-        <v>0.34</v>
+        <v>0.3849999904632568</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -10529,19 +10529,19 @@
         <v>583</v>
       </c>
       <c r="F25" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G25" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H25">
-        <v>0.194</v>
+        <v>0.2000000029802322</v>
       </c>
       <c r="I25">
-        <v>0.398</v>
+        <v>0.5320000052452087</v>
       </c>
       <c r="J25">
-        <v>0.408</v>
+        <v>0.2669999897480011</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -10561,19 +10561,19 @@
         <v>583</v>
       </c>
       <c r="F26" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G26" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H26">
-        <v>0.33</v>
+        <v>0.09399999678134918</v>
       </c>
       <c r="I26">
-        <v>0.33</v>
+        <v>0.5669999718666077</v>
       </c>
       <c r="J26">
-        <v>0.34</v>
+        <v>0.3389999866485596</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -10593,19 +10593,19 @@
         <v>583</v>
       </c>
       <c r="F27" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G27" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H27">
-        <v>0.33</v>
+        <v>0.1720000058412552</v>
       </c>
       <c r="I27">
-        <v>0.33</v>
+        <v>0.2540000081062317</v>
       </c>
       <c r="J27">
-        <v>0.34</v>
+        <v>0.5740000009536743</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -10625,19 +10625,19 @@
         <v>584</v>
       </c>
       <c r="F28" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G28" t="s">
         <v>584</v>
       </c>
       <c r="H28">
-        <v>0.33</v>
+        <v>0.1220000013709068</v>
       </c>
       <c r="I28">
-        <v>0.33</v>
+        <v>0.7390000224113464</v>
       </c>
       <c r="J28">
-        <v>0.34</v>
+        <v>0.1389999985694885</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -10657,19 +10657,19 @@
         <v>583</v>
       </c>
       <c r="F29" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G29" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H29">
-        <v>0.33</v>
+        <v>0.07800000160932541</v>
       </c>
       <c r="I29">
-        <v>0.33</v>
+        <v>0.3899999856948853</v>
       </c>
       <c r="J29">
-        <v>0.34</v>
+        <v>0.5320000052452087</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -10689,19 +10689,19 @@
         <v>584</v>
       </c>
       <c r="F30" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G30" t="s">
         <v>584</v>
       </c>
       <c r="H30">
-        <v>0.33</v>
+        <v>0.119999997317791</v>
       </c>
       <c r="I30">
-        <v>0.33</v>
+        <v>0.2560000121593475</v>
       </c>
       <c r="J30">
-        <v>0.34</v>
+        <v>0.6240000128746033</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -10721,19 +10721,19 @@
         <v>584</v>
       </c>
       <c r="F31" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G31" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H31">
-        <v>0.33</v>
+        <v>0.07199999690055847</v>
       </c>
       <c r="I31">
-        <v>0.33</v>
+        <v>0.6570000052452087</v>
       </c>
       <c r="J31">
-        <v>0.34</v>
+        <v>0.2709999978542328</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -10753,19 +10753,19 @@
         <v>584</v>
       </c>
       <c r="F32" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G32" t="s">
         <v>584</v>
       </c>
       <c r="H32">
-        <v>0.33</v>
+        <v>0.07999999821186066</v>
       </c>
       <c r="I32">
-        <v>0.33</v>
+        <v>0.5170000195503235</v>
       </c>
       <c r="J32">
-        <v>0.34</v>
+        <v>0.4029999971389771</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -10785,19 +10785,19 @@
         <v>583</v>
       </c>
       <c r="F33" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G33" t="s">
         <v>584</v>
       </c>
       <c r="H33">
-        <v>0.33</v>
+        <v>0.2049999982118607</v>
       </c>
       <c r="I33">
-        <v>0.33</v>
+        <v>0.4379999935626984</v>
       </c>
       <c r="J33">
-        <v>0.34</v>
+        <v>0.3569999933242798</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -10817,19 +10817,19 @@
         <v>583</v>
       </c>
       <c r="F34" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G34" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H34">
-        <v>0.33</v>
+        <v>0.1609999984502792</v>
       </c>
       <c r="I34">
-        <v>0.33</v>
+        <v>0.3980000019073486</v>
       </c>
       <c r="J34">
-        <v>0.34</v>
+        <v>0.4410000145435333</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -10849,19 +10849,19 @@
         <v>583</v>
       </c>
       <c r="F35" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G35" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H35">
-        <v>0.33</v>
+        <v>0.08500000089406967</v>
       </c>
       <c r="I35">
-        <v>0.33</v>
+        <v>0.578000009059906</v>
       </c>
       <c r="J35">
-        <v>0.34</v>
+        <v>0.3370000123977661</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -10881,19 +10881,19 @@
         <v>583</v>
       </c>
       <c r="F36" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G36" t="s">
         <v>584</v>
       </c>
       <c r="H36">
-        <v>0.33</v>
+        <v>0.1309999972581863</v>
       </c>
       <c r="I36">
-        <v>0.33</v>
+        <v>0.4480000138282776</v>
       </c>
       <c r="J36">
-        <v>0.34</v>
+        <v>0.4199999868869781</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -10913,19 +10913,19 @@
         <v>583</v>
       </c>
       <c r="F37" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G37" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H37">
-        <v>0.33</v>
+        <v>0.1209999993443489</v>
       </c>
       <c r="I37">
-        <v>0.33</v>
+        <v>0.4819999933242798</v>
       </c>
       <c r="J37">
-        <v>0.34</v>
+        <v>0.3970000147819519</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -10945,19 +10945,19 @@
         <v>584</v>
       </c>
       <c r="F38" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G38" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H38">
-        <v>0.33</v>
+        <v>0.1509999930858612</v>
       </c>
       <c r="I38">
-        <v>0.33</v>
+        <v>0.2049999982118607</v>
       </c>
       <c r="J38">
-        <v>0.34</v>
+        <v>0.6439999938011169</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -10977,19 +10977,19 @@
         <v>583</v>
       </c>
       <c r="F39" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G39" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H39">
-        <v>0.33</v>
+        <v>0.07000000029802322</v>
       </c>
       <c r="I39">
-        <v>0.33</v>
+        <v>0.7009999752044678</v>
       </c>
       <c r="J39">
-        <v>0.34</v>
+        <v>0.2290000021457672</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -11009,19 +11009,19 @@
         <v>584</v>
       </c>
       <c r="F40" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G40" t="s">
         <v>584</v>
       </c>
       <c r="H40">
-        <v>0.33</v>
+        <v>0.1430000066757202</v>
       </c>
       <c r="I40">
-        <v>0.33</v>
+        <v>0.2529999911785126</v>
       </c>
       <c r="J40">
-        <v>0.34</v>
+        <v>0.6039999723434448</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -11041,19 +11041,19 @@
         <v>584</v>
       </c>
       <c r="F41" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G41" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H41">
-        <v>0.33</v>
+        <v>0.1369999945163727</v>
       </c>
       <c r="I41">
-        <v>0.33</v>
+        <v>0.4390000104904175</v>
       </c>
       <c r="J41">
-        <v>0.34</v>
+        <v>0.4230000078678131</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -11073,19 +11073,19 @@
         <v>583</v>
       </c>
       <c r="F42" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G42" t="s">
         <v>584</v>
       </c>
       <c r="H42">
-        <v>0.33</v>
+        <v>0.09099999815225601</v>
       </c>
       <c r="I42">
-        <v>0.33</v>
+        <v>0.4720000028610229</v>
       </c>
       <c r="J42">
-        <v>0.34</v>
+        <v>0.4370000064373016</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -11105,19 +11105,19 @@
         <v>584</v>
       </c>
       <c r="F43" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G43" t="s">
         <v>584</v>
       </c>
       <c r="H43">
-        <v>0.33</v>
+        <v>0.09799999743700027</v>
       </c>
       <c r="I43">
-        <v>0.33</v>
+        <v>0.3260000050067902</v>
       </c>
       <c r="J43">
-        <v>0.34</v>
+        <v>0.574999988079071</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -11137,19 +11137,19 @@
         <v>584</v>
       </c>
       <c r="F44" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G44" t="s">
         <v>584</v>
       </c>
       <c r="H44">
-        <v>0.33</v>
+        <v>0.1669999957084656</v>
       </c>
       <c r="I44">
-        <v>0.33</v>
+        <v>0.2189999967813492</v>
       </c>
       <c r="J44">
-        <v>0.34</v>
+        <v>0.6140000224113464</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -11169,19 +11169,19 @@
         <v>583</v>
       </c>
       <c r="F45" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G45" t="s">
         <v>584</v>
       </c>
       <c r="H45">
-        <v>0.33</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="I45">
-        <v>0.33</v>
+        <v>0.4359999895095825</v>
       </c>
       <c r="J45">
-        <v>0.34</v>
+        <v>0.2939999997615814</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -11201,19 +11201,19 @@
         <v>583</v>
       </c>
       <c r="F46" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G46" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H46">
-        <v>0.33</v>
+        <v>0.08799999952316284</v>
       </c>
       <c r="I46">
-        <v>0.33</v>
+        <v>0.6439999938011169</v>
       </c>
       <c r="J46">
-        <v>0.34</v>
+        <v>0.2680000066757202</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -11233,19 +11233,19 @@
         <v>584</v>
       </c>
       <c r="F47" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G47" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H47">
-        <v>0.33</v>
+        <v>0.193000003695488</v>
       </c>
       <c r="I47">
-        <v>0.33</v>
+        <v>0.503000020980835</v>
       </c>
       <c r="J47">
-        <v>0.34</v>
+        <v>0.3050000071525574</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -11265,19 +11265,19 @@
         <v>583</v>
       </c>
       <c r="F48" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G48" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H48">
-        <v>0.33</v>
+        <v>0.1790000051259995</v>
       </c>
       <c r="I48">
-        <v>0.33</v>
+        <v>0.5690000057220459</v>
       </c>
       <c r="J48">
-        <v>0.34</v>
+        <v>0.2520000040531158</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -11297,19 +11297,19 @@
         <v>584</v>
       </c>
       <c r="F49" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G49" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H49">
-        <v>0.33</v>
+        <v>0.1209999993443489</v>
       </c>
       <c r="I49">
-        <v>0.33</v>
+        <v>0.4169999957084656</v>
       </c>
       <c r="J49">
-        <v>0.34</v>
+        <v>0.4620000123977661</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -11329,19 +11329,19 @@
         <v>583</v>
       </c>
       <c r="F50" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G50" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H50">
-        <v>0.33</v>
+        <v>0.2630000114440918</v>
       </c>
       <c r="I50">
-        <v>0.33</v>
+        <v>0.4950000047683716</v>
       </c>
       <c r="J50">
-        <v>0.34</v>
+        <v>0.2409999966621399</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -11361,19 +11361,19 @@
         <v>583</v>
       </c>
       <c r="F51" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G51" t="s">
         <v>584</v>
       </c>
       <c r="H51">
-        <v>0.33</v>
+        <v>0.1430000066757202</v>
       </c>
       <c r="I51">
-        <v>0.33</v>
+        <v>0.550000011920929</v>
       </c>
       <c r="J51">
-        <v>0.34</v>
+        <v>0.3070000112056732</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -11393,19 +11393,19 @@
         <v>583</v>
       </c>
       <c r="F52" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G52" t="s">
         <v>584</v>
       </c>
       <c r="H52">
-        <v>0.33</v>
+        <v>0.07599999755620956</v>
       </c>
       <c r="I52">
-        <v>0.33</v>
+        <v>0.3659999966621399</v>
       </c>
       <c r="J52">
-        <v>0.34</v>
+        <v>0.5580000281333923</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -11425,19 +11425,19 @@
         <v>584</v>
       </c>
       <c r="F53" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G53" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H53">
-        <v>0.33</v>
+        <v>0.07999999821186066</v>
       </c>
       <c r="I53">
-        <v>0.33</v>
+        <v>0.5220000147819519</v>
       </c>
       <c r="J53">
-        <v>0.34</v>
+        <v>0.3980000019073486</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -11457,19 +11457,19 @@
         <v>583</v>
       </c>
       <c r="F54" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G54" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H54">
-        <v>0.33</v>
+        <v>0.1700000017881393</v>
       </c>
       <c r="I54">
-        <v>0.33</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="J54">
-        <v>0.34</v>
+        <v>0.2000000029802322</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -11489,19 +11489,19 @@
         <v>583</v>
       </c>
       <c r="F55" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G55" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H55">
-        <v>0.33</v>
+        <v>0.09300000220537186</v>
       </c>
       <c r="I55">
-        <v>0.33</v>
+        <v>0.5490000247955322</v>
       </c>
       <c r="J55">
-        <v>0.34</v>
+        <v>0.3580000102519989</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -11521,19 +11521,19 @@
         <v>584</v>
       </c>
       <c r="F56" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G56" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H56">
-        <v>0.33</v>
+        <v>0.1669999957084656</v>
       </c>
       <c r="I56">
-        <v>0.33</v>
+        <v>0.4339999854564667</v>
       </c>
       <c r="J56">
-        <v>0.34</v>
+        <v>0.3989999890327454</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -11553,19 +11553,19 @@
         <v>584</v>
       </c>
       <c r="F57" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G57" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H57">
-        <v>0.33</v>
+        <v>0.1430000066757202</v>
       </c>
       <c r="I57">
-        <v>0.33</v>
+        <v>0.3409999907016754</v>
       </c>
       <c r="J57">
-        <v>0.34</v>
+        <v>0.515999972820282</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -11585,19 +11585,19 @@
         <v>584</v>
       </c>
       <c r="F58" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G58" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H58">
-        <v>0.33</v>
+        <v>0.07500000298023224</v>
       </c>
       <c r="I58">
-        <v>0.33</v>
+        <v>0.5929999947547913</v>
       </c>
       <c r="J58">
-        <v>0.34</v>
+        <v>0.3319999873638153</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -11617,19 +11617,19 @@
         <v>584</v>
       </c>
       <c r="F59" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G59" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H59">
-        <v>0.33</v>
+        <v>0.1780000030994415</v>
       </c>
       <c r="I59">
-        <v>0.33</v>
+        <v>0.5720000267028809</v>
       </c>
       <c r="J59">
-        <v>0.34</v>
+        <v>0.2509999871253967</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -11649,19 +11649,19 @@
         <v>583</v>
       </c>
       <c r="F60" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G60" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H60">
-        <v>0.33</v>
+        <v>0.2949999868869781</v>
       </c>
       <c r="I60">
-        <v>0.33</v>
+        <v>0.1190000027418137</v>
       </c>
       <c r="J60">
-        <v>0.34</v>
+        <v>0.5849999785423279</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -11681,19 +11681,19 @@
         <v>583</v>
       </c>
       <c r="F61" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G61" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H61">
-        <v>0.33</v>
+        <v>0.07699999958276749</v>
       </c>
       <c r="I61">
-        <v>0.33</v>
+        <v>0.5929999947547913</v>
       </c>
       <c r="J61">
-        <v>0.34</v>
+        <v>0.3310000002384186</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -11713,19 +11713,19 @@
         <v>583</v>
       </c>
       <c r="F62" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G62" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H62">
-        <v>0.33</v>
+        <v>0.09200000017881393</v>
       </c>
       <c r="I62">
-        <v>0.33</v>
+        <v>0.656000018119812</v>
       </c>
       <c r="J62">
-        <v>0.34</v>
+        <v>0.2520000040531158</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -11751,13 +11751,13 @@
         <v>584</v>
       </c>
       <c r="H63">
-        <v>0.33</v>
+        <v>0.4460000097751617</v>
       </c>
       <c r="I63">
-        <v>0.33</v>
+        <v>0.1580000072717667</v>
       </c>
       <c r="J63">
-        <v>0.34</v>
+        <v>0.3959999978542328</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -11777,19 +11777,19 @@
         <v>584</v>
       </c>
       <c r="F64" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G64" t="s">
         <v>584</v>
       </c>
       <c r="H64">
-        <v>0.33</v>
+        <v>0.1059999987483025</v>
       </c>
       <c r="I64">
-        <v>0.33</v>
+        <v>0.3429999947547913</v>
       </c>
       <c r="J64">
-        <v>0.34</v>
+        <v>0.5509999990463257</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -11809,19 +11809,19 @@
         <v>584</v>
       </c>
       <c r="F65" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G65" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H65">
-        <v>0.33</v>
+        <v>0.07299999892711639</v>
       </c>
       <c r="I65">
-        <v>0.33</v>
+        <v>0.5189999938011169</v>
       </c>
       <c r="J65">
-        <v>0.34</v>
+        <v>0.4079999923706055</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -11841,19 +11841,19 @@
         <v>583</v>
       </c>
       <c r="F66" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H66">
-        <v>0.33</v>
+        <v>0.0989999994635582</v>
       </c>
       <c r="I66">
-        <v>0.33</v>
+        <v>0.4659999907016754</v>
       </c>
       <c r="J66">
-        <v>0.34</v>
+        <v>0.4339999854564667</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -11873,19 +11873,19 @@
         <v>583</v>
       </c>
       <c r="F67" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G67" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H67">
-        <v>0.33</v>
+        <v>0.0820000022649765</v>
       </c>
       <c r="I67">
-        <v>0.33</v>
+        <v>0.367000013589859</v>
       </c>
       <c r="J67">
-        <v>0.34</v>
+        <v>0.5509999990463257</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -11905,19 +11905,19 @@
         <v>584</v>
       </c>
       <c r="F68" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G68" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H68">
-        <v>0.33</v>
+        <v>0.1400000005960464</v>
       </c>
       <c r="I68">
-        <v>0.33</v>
+        <v>0.3519999980926514</v>
       </c>
       <c r="J68">
-        <v>0.34</v>
+        <v>0.5080000162124634</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -11937,19 +11937,19 @@
         <v>583</v>
       </c>
       <c r="F69" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G69" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H69">
-        <v>0.33</v>
+        <v>0.135000005364418</v>
       </c>
       <c r="I69">
-        <v>0.33</v>
+        <v>0.3610000014305115</v>
       </c>
       <c r="J69">
-        <v>0.34</v>
+        <v>0.5040000081062317</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -11969,19 +11969,19 @@
         <v>584</v>
       </c>
       <c r="F70" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G70" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H70">
-        <v>0.33</v>
+        <v>0.1439999938011169</v>
       </c>
       <c r="I70">
-        <v>0.33</v>
+        <v>0.4149999916553497</v>
       </c>
       <c r="J70">
-        <v>0.34</v>
+        <v>0.4410000145435333</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -12001,19 +12001,19 @@
         <v>583</v>
       </c>
       <c r="F71" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G71" t="s">
         <v>584</v>
       </c>
       <c r="H71">
-        <v>0.33</v>
+        <v>0.1909999996423721</v>
       </c>
       <c r="I71">
-        <v>0.33</v>
+        <v>0.5450000166893005</v>
       </c>
       <c r="J71">
-        <v>0.34</v>
+        <v>0.2639999985694885</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -12033,19 +12033,19 @@
         <v>583</v>
       </c>
       <c r="F72" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G72" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H72">
-        <v>0.33</v>
+        <v>0.1089999973773956</v>
       </c>
       <c r="I72">
-        <v>0.33</v>
+        <v>0.488999992609024</v>
       </c>
       <c r="J72">
-        <v>0.34</v>
+        <v>0.4020000100135803</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -12065,19 +12065,19 @@
         <v>583</v>
       </c>
       <c r="F73" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G73" t="s">
         <v>584</v>
       </c>
       <c r="H73">
-        <v>0.33</v>
+        <v>0.1889999955892563</v>
       </c>
       <c r="I73">
-        <v>0.33</v>
+        <v>0.425000011920929</v>
       </c>
       <c r="J73">
-        <v>0.34</v>
+        <v>0.386000007390976</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -12097,19 +12097,19 @@
         <v>584</v>
       </c>
       <c r="F74" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G74" t="s">
         <v>584</v>
       </c>
       <c r="H74">
-        <v>0.33</v>
+        <v>0.1140000000596046</v>
       </c>
       <c r="I74">
-        <v>0.33</v>
+        <v>0.4149999916553497</v>
       </c>
       <c r="J74">
-        <v>0.34</v>
+        <v>0.4709999859333038</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -12129,19 +12129,19 @@
         <v>584</v>
       </c>
       <c r="F75" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G75" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H75">
-        <v>0.33</v>
+        <v>0.1319999992847443</v>
       </c>
       <c r="I75">
-        <v>0.33</v>
+        <v>0.4329999983310699</v>
       </c>
       <c r="J75">
-        <v>0.34</v>
+        <v>0.4339999854564667</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -12161,19 +12161,19 @@
         <v>584</v>
       </c>
       <c r="F76" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G76" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H76">
-        <v>0.33</v>
+        <v>0.1659999936819077</v>
       </c>
       <c r="I76">
-        <v>0.33</v>
+        <v>0.5090000033378601</v>
       </c>
       <c r="J76">
-        <v>0.34</v>
+        <v>0.324999988079071</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -12193,19 +12193,19 @@
         <v>583</v>
       </c>
       <c r="F77" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G77" t="s">
         <v>584</v>
       </c>
       <c r="H77">
-        <v>0.33</v>
+        <v>0.1659999936819077</v>
       </c>
       <c r="I77">
-        <v>0.33</v>
+        <v>0.2619999945163727</v>
       </c>
       <c r="J77">
-        <v>0.34</v>
+        <v>0.5709999799728394</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -12222,19 +12222,19 @@
         <v>583</v>
       </c>
       <c r="F78" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G78" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H78">
-        <v>0.33</v>
+        <v>0.08299999684095383</v>
       </c>
       <c r="I78">
-        <v>0.33</v>
+        <v>0.6359999775886536</v>
       </c>
       <c r="J78">
-        <v>0.34</v>
+        <v>0.2809999883174896</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -12254,19 +12254,19 @@
         <v>583</v>
       </c>
       <c r="F79" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G79" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H79">
-        <v>0.33</v>
+        <v>0.07199999690055847</v>
       </c>
       <c r="I79">
-        <v>0.33</v>
+        <v>0.6759999990463257</v>
       </c>
       <c r="J79">
-        <v>0.34</v>
+        <v>0.2520000040531158</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -12286,19 +12286,19 @@
         <v>584</v>
       </c>
       <c r="F80" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G80" t="s">
         <v>584</v>
       </c>
       <c r="H80">
-        <v>0.33</v>
+        <v>0.09300000220537186</v>
       </c>
       <c r="I80">
-        <v>0.33</v>
+        <v>0.421999990940094</v>
       </c>
       <c r="J80">
-        <v>0.34</v>
+        <v>0.4839999973773956</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -12318,19 +12318,19 @@
         <v>583</v>
       </c>
       <c r="F81" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G81" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H81">
-        <v>0.33</v>
+        <v>0.1019999980926514</v>
       </c>
       <c r="I81">
-        <v>0.33</v>
+        <v>0.6230000257492065</v>
       </c>
       <c r="J81">
-        <v>0.34</v>
+        <v>0.2750000059604645</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -12350,19 +12350,19 @@
         <v>583</v>
       </c>
       <c r="F82" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G82" t="s">
         <v>584</v>
       </c>
       <c r="H82">
-        <v>0.33</v>
+        <v>0.09399999678134918</v>
       </c>
       <c r="I82">
-        <v>0.33</v>
+        <v>0.4709999859333038</v>
       </c>
       <c r="J82">
-        <v>0.34</v>
+        <v>0.4350000023841858</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -12382,19 +12382,19 @@
         <v>584</v>
       </c>
       <c r="F83" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G83" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H83">
-        <v>0.33</v>
+        <v>0.08600000292062759</v>
       </c>
       <c r="I83">
-        <v>0.33</v>
+        <v>0.574999988079071</v>
       </c>
       <c r="J83">
-        <v>0.34</v>
+        <v>0.3389999866485596</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -12414,19 +12414,19 @@
         <v>583</v>
       </c>
       <c r="F84" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G84" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H84">
-        <v>0.33</v>
+        <v>0.193000003695488</v>
       </c>
       <c r="I84">
-        <v>0.33</v>
+        <v>0.3100000023841858</v>
       </c>
       <c r="J84">
-        <v>0.34</v>
+        <v>0.4970000088214874</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -12446,19 +12446,19 @@
         <v>584</v>
       </c>
       <c r="F85" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G85" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H85">
-        <v>0.33</v>
+        <v>0.1099999994039536</v>
       </c>
       <c r="I85">
-        <v>0.33</v>
+        <v>0.593999981880188</v>
       </c>
       <c r="J85">
-        <v>0.34</v>
+        <v>0.2960000038146973</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -12478,19 +12478,19 @@
         <v>583</v>
       </c>
       <c r="F86" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G86" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H86">
-        <v>0.33</v>
+        <v>0.1710000038146973</v>
       </c>
       <c r="I86">
-        <v>0.33</v>
+        <v>0.5740000009536743</v>
       </c>
       <c r="J86">
-        <v>0.34</v>
+        <v>0.2549999952316284</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -12510,19 +12510,19 @@
         <v>584</v>
       </c>
       <c r="F87" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G87" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H87">
-        <v>0.33</v>
+        <v>0.08399999886751175</v>
       </c>
       <c r="I87">
-        <v>0.33</v>
+        <v>0.4580000042915344</v>
       </c>
       <c r="J87">
-        <v>0.34</v>
+        <v>0.4580000042915344</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -12542,19 +12542,19 @@
         <v>583</v>
       </c>
       <c r="F88" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G88" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H88">
-        <v>0.33</v>
+        <v>0.07800000160932541</v>
       </c>
       <c r="I88">
-        <v>0.33</v>
+        <v>0.4510000050067902</v>
       </c>
       <c r="J88">
-        <v>0.34</v>
+        <v>0.4709999859333038</v>
       </c>
     </row>
     <row r="89" spans="1:10">
@@ -12574,19 +12574,19 @@
         <v>584</v>
       </c>
       <c r="F89" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G89" t="s">
         <v>584</v>
       </c>
       <c r="H89">
-        <v>0.33</v>
+        <v>0.119999997317791</v>
       </c>
       <c r="I89">
-        <v>0.33</v>
+        <v>0.5529999732971191</v>
       </c>
       <c r="J89">
-        <v>0.34</v>
+        <v>0.3269999921321869</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -12606,19 +12606,19 @@
         <v>583</v>
       </c>
       <c r="F90" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G90" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H90">
-        <v>0.33</v>
+        <v>0.1780000030994415</v>
       </c>
       <c r="I90">
-        <v>0.33</v>
+        <v>0.2860000133514404</v>
       </c>
       <c r="J90">
-        <v>0.34</v>
+        <v>0.5360000133514404</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -12638,19 +12638,19 @@
         <v>583</v>
       </c>
       <c r="F91" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G91" t="s">
         <v>584</v>
       </c>
       <c r="H91">
-        <v>0.33</v>
+        <v>0.07699999958276749</v>
       </c>
       <c r="I91">
-        <v>0.33</v>
+        <v>0.5189999938011169</v>
       </c>
       <c r="J91">
-        <v>0.34</v>
+        <v>0.4040000140666962</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -12670,19 +12670,19 @@
         <v>584</v>
       </c>
       <c r="F92" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G92" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H92">
-        <v>0.33</v>
+        <v>0.1040000021457672</v>
       </c>
       <c r="I92">
-        <v>0.33</v>
+        <v>0.4300000071525574</v>
       </c>
       <c r="J92">
-        <v>0.34</v>
+        <v>0.4659999907016754</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -12702,19 +12702,19 @@
         <v>583</v>
       </c>
       <c r="F93" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G93" t="s">
         <v>584</v>
       </c>
       <c r="H93">
-        <v>0.33</v>
+        <v>0.07199999690055847</v>
       </c>
       <c r="I93">
-        <v>0.33</v>
+        <v>0.4269999861717224</v>
       </c>
       <c r="J93">
-        <v>0.34</v>
+        <v>0.5009999871253967</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -12734,19 +12734,19 @@
         <v>584</v>
       </c>
       <c r="F94" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G94" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H94">
-        <v>0.33</v>
+        <v>0.1650000065565109</v>
       </c>
       <c r="I94">
-        <v>0.33</v>
+        <v>0.1720000058412552</v>
       </c>
       <c r="J94">
-        <v>0.34</v>
+        <v>0.6620000004768372</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -12766,19 +12766,19 @@
         <v>583</v>
       </c>
       <c r="F95" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G95" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H95">
-        <v>0.33</v>
+        <v>0.1080000028014183</v>
       </c>
       <c r="I95">
-        <v>0.33</v>
+        <v>0.4059999883174896</v>
       </c>
       <c r="J95">
-        <v>0.34</v>
+        <v>0.4860000014305115</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -12798,19 +12798,19 @@
         <v>583</v>
       </c>
       <c r="F96" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G96" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H96">
-        <v>0.33</v>
+        <v>0.1469999998807907</v>
       </c>
       <c r="I96">
-        <v>0.33</v>
+        <v>0.1899999976158142</v>
       </c>
       <c r="J96">
-        <v>0.34</v>
+        <v>0.6629999876022339</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -12830,19 +12830,19 @@
         <v>583</v>
       </c>
       <c r="F97" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G97" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H97">
-        <v>0.33</v>
+        <v>0.1469999998807907</v>
       </c>
       <c r="I97">
-        <v>0.33</v>
+        <v>0.628000020980835</v>
       </c>
       <c r="J97">
-        <v>0.34</v>
+        <v>0.2249999940395355</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -12862,19 +12862,19 @@
         <v>583</v>
       </c>
       <c r="F98" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G98" t="s">
         <v>584</v>
       </c>
       <c r="H98">
-        <v>0.33</v>
+        <v>0.1089999973773956</v>
       </c>
       <c r="I98">
-        <v>0.33</v>
+        <v>0.3729999959468842</v>
       </c>
       <c r="J98">
-        <v>0.34</v>
+        <v>0.5180000066757202</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -12894,19 +12894,19 @@
         <v>584</v>
       </c>
       <c r="F99" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G99" t="s">
         <v>584</v>
       </c>
       <c r="H99">
-        <v>0.33</v>
+        <v>0.1739999949932098</v>
       </c>
       <c r="I99">
-        <v>0.33</v>
+        <v>0.3459999859333038</v>
       </c>
       <c r="J99">
-        <v>0.34</v>
+        <v>0.4799999892711639</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -12926,19 +12926,19 @@
         <v>583</v>
       </c>
       <c r="F100" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G100" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H100">
-        <v>0.33</v>
+        <v>0.0689999982714653</v>
       </c>
       <c r="I100">
-        <v>0.33</v>
+        <v>0.6779999732971191</v>
       </c>
       <c r="J100">
-        <v>0.34</v>
+        <v>0.2529999911785126</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -12958,19 +12958,19 @@
         <v>583</v>
       </c>
       <c r="F101" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G101" t="s">
         <v>584</v>
       </c>
       <c r="H101">
-        <v>0.33</v>
+        <v>0.08900000154972076</v>
       </c>
       <c r="I101">
-        <v>0.33</v>
+        <v>0.4729999899864197</v>
       </c>
       <c r="J101">
-        <v>0.34</v>
+        <v>0.4379999935626984</v>
       </c>
     </row>
     <row r="102" spans="1:10">
@@ -12990,19 +12990,19 @@
         <v>583</v>
       </c>
       <c r="F102" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G102" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H102">
-        <v>0.33</v>
+        <v>0.136000007390976</v>
       </c>
       <c r="I102">
-        <v>0.33</v>
+        <v>0.3339999914169312</v>
       </c>
       <c r="J102">
-        <v>0.34</v>
+        <v>0.5299999713897705</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -13022,19 +13022,19 @@
         <v>583</v>
       </c>
       <c r="F103" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G103" t="s">
         <v>584</v>
       </c>
       <c r="H103">
-        <v>0.33</v>
+        <v>0.1150000020861626</v>
       </c>
       <c r="I103">
-        <v>0.33</v>
+        <v>0.5960000157356262</v>
       </c>
       <c r="J103">
-        <v>0.34</v>
+        <v>0.289000004529953</v>
       </c>
     </row>
     <row r="104" spans="1:10">
@@ -13054,19 +13054,19 @@
         <v>584</v>
       </c>
       <c r="F104" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G104" t="s">
         <v>584</v>
       </c>
       <c r="H104">
-        <v>0.33</v>
+        <v>0.08299999684095383</v>
       </c>
       <c r="I104">
-        <v>0.33</v>
+        <v>0.6420000195503235</v>
       </c>
       <c r="J104">
-        <v>0.34</v>
+        <v>0.2750000059604645</v>
       </c>
     </row>
     <row r="105" spans="1:10">
@@ -13086,19 +13086,19 @@
         <v>583</v>
       </c>
       <c r="F105" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G105" t="s">
         <v>584</v>
       </c>
       <c r="H105">
-        <v>0.33</v>
+        <v>0.07400000095367432</v>
       </c>
       <c r="I105">
-        <v>0.33</v>
+        <v>0.5410000085830688</v>
       </c>
       <c r="J105">
-        <v>0.34</v>
+        <v>0.3849999904632568</v>
       </c>
     </row>
     <row r="106" spans="1:10">
@@ -13118,19 +13118,19 @@
         <v>583</v>
       </c>
       <c r="F106" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G106" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H106">
-        <v>0.33</v>
+        <v>0.1729999929666519</v>
       </c>
       <c r="I106">
-        <v>0.33</v>
+        <v>0.2189999967813492</v>
       </c>
       <c r="J106">
-        <v>0.34</v>
+        <v>0.609000027179718</v>
       </c>
     </row>
     <row r="107" spans="1:10">
@@ -13150,19 +13150,19 @@
         <v>583</v>
       </c>
       <c r="F107" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G107" t="s">
         <v>584</v>
       </c>
       <c r="H107">
-        <v>0.33</v>
+        <v>0.09300000220537186</v>
       </c>
       <c r="I107">
-        <v>0.33</v>
+        <v>0.4429999887943268</v>
       </c>
       <c r="J107">
-        <v>0.34</v>
+        <v>0.4629999995231628</v>
       </c>
     </row>
     <row r="108" spans="1:10">
@@ -13182,19 +13182,19 @@
         <v>583</v>
       </c>
       <c r="F108" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G108" t="s">
         <v>584</v>
       </c>
       <c r="H108">
-        <v>0.33</v>
+        <v>0.1209999993443489</v>
       </c>
       <c r="I108">
-        <v>0.33</v>
+        <v>0.5040000081062317</v>
       </c>
       <c r="J108">
-        <v>0.34</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="109" spans="1:10">
@@ -13214,19 +13214,19 @@
         <v>583</v>
       </c>
       <c r="F109" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G109" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H109">
-        <v>0.33</v>
+        <v>0.1920000016689301</v>
       </c>
       <c r="I109">
-        <v>0.33</v>
+        <v>0.6039999723434448</v>
       </c>
       <c r="J109">
-        <v>0.34</v>
+        <v>0.2039999961853027</v>
       </c>
     </row>
     <row r="110" spans="1:10">
@@ -13246,19 +13246,19 @@
         <v>584</v>
       </c>
       <c r="F110" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G110" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H110">
-        <v>0.33</v>
+        <v>0.07999999821186066</v>
       </c>
       <c r="I110">
-        <v>0.33</v>
+        <v>0.6050000190734863</v>
       </c>
       <c r="J110">
-        <v>0.34</v>
+        <v>0.3149999976158142</v>
       </c>
     </row>
     <row r="111" spans="1:10">
@@ -13278,19 +13278,19 @@
         <v>583</v>
       </c>
       <c r="F111" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G111" t="s">
         <v>584</v>
       </c>
       <c r="H111">
-        <v>0.33</v>
+        <v>0.1319999992847443</v>
       </c>
       <c r="I111">
-        <v>0.33</v>
+        <v>0.7160000205039978</v>
       </c>
       <c r="J111">
-        <v>0.34</v>
+        <v>0.1529999971389771</v>
       </c>
     </row>
     <row r="112" spans="1:10">
@@ -13310,19 +13310,19 @@
         <v>583</v>
       </c>
       <c r="F112" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G112" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H112">
-        <v>0.33</v>
+        <v>0.09399999678134918</v>
       </c>
       <c r="I112">
-        <v>0.33</v>
+        <v>0.453000009059906</v>
       </c>
       <c r="J112">
-        <v>0.34</v>
+        <v>0.453000009059906</v>
       </c>
     </row>
     <row r="113" spans="1:10">
@@ -13342,19 +13342,19 @@
         <v>583</v>
       </c>
       <c r="F113" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G113" t="s">
         <v>584</v>
       </c>
       <c r="H113">
-        <v>0.33</v>
+        <v>0.07699999958276749</v>
       </c>
       <c r="I113">
-        <v>0.33</v>
+        <v>0.578000009059906</v>
       </c>
       <c r="J113">
-        <v>0.34</v>
+        <v>0.3449999988079071</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -13374,19 +13374,19 @@
         <v>583</v>
       </c>
       <c r="F114" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G114" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H114">
-        <v>0.33</v>
+        <v>0.1220000013709068</v>
       </c>
       <c r="I114">
-        <v>0.33</v>
+        <v>0.4560000002384186</v>
       </c>
       <c r="J114">
-        <v>0.34</v>
+        <v>0.421999990940094</v>
       </c>
     </row>
     <row r="115" spans="1:10">
@@ -13406,19 +13406,19 @@
         <v>583</v>
       </c>
       <c r="F115" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G115" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H115">
-        <v>0.33</v>
+        <v>0.07199999690055847</v>
       </c>
       <c r="I115">
-        <v>0.33</v>
+        <v>0.3959999978542328</v>
       </c>
       <c r="J115">
-        <v>0.34</v>
+        <v>0.531000018119812</v>
       </c>
     </row>
     <row r="116" spans="1:10">
@@ -13438,19 +13438,19 @@
         <v>583</v>
       </c>
       <c r="F116" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G116" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H116">
-        <v>0.33</v>
+        <v>0.1739999949932098</v>
       </c>
       <c r="I116">
-        <v>0.33</v>
+        <v>0.5450000166893005</v>
       </c>
       <c r="J116">
-        <v>0.34</v>
+        <v>0.2809999883174896</v>
       </c>
     </row>
     <row r="117" spans="1:10">
@@ -13470,19 +13470,19 @@
         <v>584</v>
       </c>
       <c r="F117" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G117" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H117">
-        <v>0.33</v>
+        <v>0.07900000363588333</v>
       </c>
       <c r="I117">
-        <v>0.33</v>
+        <v>0.6349999904632568</v>
       </c>
       <c r="J117">
-        <v>0.34</v>
+        <v>0.2860000133514404</v>
       </c>
     </row>
     <row r="118" spans="1:10">
@@ -13502,19 +13502,19 @@
         <v>583</v>
       </c>
       <c r="F118" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G118" t="s">
         <v>584</v>
       </c>
       <c r="H118">
-        <v>0.33</v>
+        <v>0.08399999886751175</v>
       </c>
       <c r="I118">
-        <v>0.33</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="J118">
-        <v>0.34</v>
+        <v>0.4059999883174896</v>
       </c>
     </row>
     <row r="119" spans="1:10">
@@ -13534,19 +13534,19 @@
         <v>583</v>
       </c>
       <c r="F119" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G119" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H119">
-        <v>0.33</v>
+        <v>0.07500000298023224</v>
       </c>
       <c r="I119">
-        <v>0.33</v>
+        <v>0.6740000247955322</v>
       </c>
       <c r="J119">
-        <v>0.34</v>
+        <v>0.2509999871253967</v>
       </c>
     </row>
     <row r="120" spans="1:10">
@@ -13566,19 +13566,19 @@
         <v>584</v>
       </c>
       <c r="F120" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G120" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H120">
-        <v>0.33</v>
+        <v>0.07199999690055847</v>
       </c>
       <c r="I120">
-        <v>0.33</v>
+        <v>0.6489999890327454</v>
       </c>
       <c r="J120">
-        <v>0.34</v>
+        <v>0.2790000140666962</v>
       </c>
     </row>
     <row r="121" spans="1:10">
@@ -13595,19 +13595,19 @@
         <v>583</v>
       </c>
       <c r="F121" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G121" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H121">
-        <v>0.33</v>
+        <v>0.1749999970197678</v>
       </c>
       <c r="I121">
-        <v>0.33</v>
+        <v>0.4410000145435333</v>
       </c>
       <c r="J121">
-        <v>0.34</v>
+        <v>0.3840000033378601</v>
       </c>
     </row>
     <row r="122" spans="1:10">
@@ -13627,19 +13627,19 @@
         <v>583</v>
       </c>
       <c r="F122" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G122" t="s">
         <v>584</v>
       </c>
       <c r="H122">
-        <v>0.33</v>
+        <v>0.1669999957084656</v>
       </c>
       <c r="I122">
-        <v>0.33</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="J122">
-        <v>0.34</v>
+        <v>0.3630000054836273</v>
       </c>
     </row>
     <row r="123" spans="1:10">
@@ -13659,19 +13659,19 @@
         <v>583</v>
       </c>
       <c r="F123" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G123" t="s">
         <v>584</v>
       </c>
       <c r="H123">
-        <v>0.33</v>
+        <v>0.1180000007152557</v>
       </c>
       <c r="I123">
-        <v>0.33</v>
+        <v>0.4480000138282776</v>
       </c>
       <c r="J123">
-        <v>0.34</v>
+        <v>0.4329999983310699</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -13691,19 +13691,19 @@
         <v>583</v>
       </c>
       <c r="F124" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G124" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H124">
-        <v>0.33</v>
+        <v>0.2879999876022339</v>
       </c>
       <c r="I124">
-        <v>0.33</v>
+        <v>0.3930000066757202</v>
       </c>
       <c r="J124">
-        <v>0.34</v>
+        <v>0.3199999928474426</v>
       </c>
     </row>
     <row r="125" spans="1:10">
@@ -13723,19 +13723,19 @@
         <v>583</v>
       </c>
       <c r="F125" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G125" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H125">
-        <v>0.33</v>
+        <v>0.1400000005960464</v>
       </c>
       <c r="I125">
-        <v>0.33</v>
+        <v>0.4169999957084656</v>
       </c>
       <c r="J125">
-        <v>0.34</v>
+        <v>0.4429999887943268</v>
       </c>
     </row>
     <row r="126" spans="1:10">
@@ -13755,19 +13755,19 @@
         <v>584</v>
       </c>
       <c r="F126" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G126" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H126">
-        <v>0.33</v>
+        <v>0.1159999966621399</v>
       </c>
       <c r="I126">
-        <v>0.33</v>
+        <v>0.3179999887943268</v>
       </c>
       <c r="J126">
-        <v>0.34</v>
+        <v>0.5659999847412109</v>
       </c>
     </row>
     <row r="127" spans="1:10">
@@ -13787,19 +13787,19 @@
         <v>583</v>
       </c>
       <c r="F127" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G127" t="s">
         <v>584</v>
       </c>
       <c r="H127">
-        <v>0.33</v>
+        <v>0.1319999992847443</v>
       </c>
       <c r="I127">
-        <v>0.33</v>
+        <v>0.5450000166893005</v>
       </c>
       <c r="J127">
-        <v>0.34</v>
+        <v>0.3219999969005585</v>
       </c>
     </row>
     <row r="128" spans="1:10">
@@ -13819,19 +13819,19 @@
         <v>584</v>
       </c>
       <c r="F128" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G128" t="s">
         <v>584</v>
       </c>
       <c r="H128">
-        <v>0.33</v>
+        <v>0.1620000004768372</v>
       </c>
       <c r="I128">
-        <v>0.33</v>
+        <v>0.2049999982118607</v>
       </c>
       <c r="J128">
-        <v>0.34</v>
+        <v>0.6330000162124634</v>
       </c>
     </row>
     <row r="129" spans="1:10">
@@ -13851,19 +13851,19 @@
         <v>583</v>
       </c>
       <c r="F129" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G129" t="s">
         <v>584</v>
       </c>
       <c r="H129">
-        <v>0.33</v>
+        <v>0.08399999886751175</v>
       </c>
       <c r="I129">
-        <v>0.33</v>
+        <v>0.453000009059906</v>
       </c>
       <c r="J129">
-        <v>0.34</v>
+        <v>0.4620000123977661</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -13883,19 +13883,19 @@
         <v>583</v>
       </c>
       <c r="F130" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G130" t="s">
         <v>584</v>
       </c>
       <c r="H130">
-        <v>0.33</v>
+        <v>0.08500000089406967</v>
       </c>
       <c r="I130">
-        <v>0.33</v>
+        <v>0.4670000076293945</v>
       </c>
       <c r="J130">
-        <v>0.34</v>
+        <v>0.4480000138282776</v>
       </c>
     </row>
     <row r="131" spans="1:10">
@@ -13915,19 +13915,19 @@
         <v>583</v>
       </c>
       <c r="F131" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G131" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H131">
-        <v>0.33</v>
+        <v>0.1260000020265579</v>
       </c>
       <c r="I131">
-        <v>0.33</v>
+        <v>0.4189999997615814</v>
       </c>
       <c r="J131">
-        <v>0.34</v>
+        <v>0.4550000131130219</v>
       </c>
     </row>
     <row r="132" spans="1:10">
@@ -13947,19 +13947,19 @@
         <v>583</v>
       </c>
       <c r="F132" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G132" t="s">
         <v>584</v>
       </c>
       <c r="H132">
-        <v>0.33</v>
+        <v>0.08500000089406967</v>
       </c>
       <c r="I132">
-        <v>0.33</v>
+        <v>0.5540000200271606</v>
       </c>
       <c r="J132">
-        <v>0.34</v>
+        <v>0.3610000014305115</v>
       </c>
     </row>
     <row r="133" spans="1:10">
@@ -13979,19 +13979,19 @@
         <v>583</v>
       </c>
       <c r="F133" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G133" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H133">
-        <v>0.33</v>
+        <v>0.07500000298023224</v>
       </c>
       <c r="I133">
-        <v>0.33</v>
+        <v>0.2790000140666962</v>
       </c>
       <c r="J133">
-        <v>0.34</v>
+        <v>0.6449999809265137</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -14011,19 +14011,19 @@
         <v>584</v>
       </c>
       <c r="F134" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G134" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H134">
-        <v>0.33</v>
+        <v>0.2419999986886978</v>
       </c>
       <c r="I134">
-        <v>0.33</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="J134">
-        <v>0.34</v>
+        <v>0.2489999979734421</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -14043,19 +14043,19 @@
         <v>583</v>
       </c>
       <c r="F135" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G135" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H135">
-        <v>0.33</v>
+        <v>0.1309999972581863</v>
       </c>
       <c r="I135">
-        <v>0.33</v>
+        <v>0.2300000041723251</v>
       </c>
       <c r="J135">
-        <v>0.34</v>
+        <v>0.6380000114440918</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -14075,19 +14075,19 @@
         <v>583</v>
       </c>
       <c r="F136" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G136" t="s">
         <v>584</v>
       </c>
       <c r="H136">
-        <v>0.33</v>
+        <v>0.1129999980330467</v>
       </c>
       <c r="I136">
-        <v>0.33</v>
+        <v>0.5609999895095825</v>
       </c>
       <c r="J136">
-        <v>0.34</v>
+        <v>0.3260000050067902</v>
       </c>
     </row>
     <row r="137" spans="1:10">
@@ -14107,19 +14107,19 @@
         <v>584</v>
       </c>
       <c r="F137" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G137" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H137">
-        <v>0.33</v>
+        <v>0.1099999994039536</v>
       </c>
       <c r="I137">
-        <v>0.33</v>
+        <v>0.5929999947547913</v>
       </c>
       <c r="J137">
-        <v>0.34</v>
+        <v>0.296999990940094</v>
       </c>
     </row>
     <row r="138" spans="1:10">
@@ -14139,19 +14139,19 @@
         <v>583</v>
       </c>
       <c r="F138" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G138" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H138">
-        <v>0.33</v>
+        <v>0.1089999973773956</v>
       </c>
       <c r="I138">
-        <v>0.33</v>
+        <v>0.2029999941587448</v>
       </c>
       <c r="J138">
-        <v>0.34</v>
+        <v>0.6880000233650208</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -14171,19 +14171,19 @@
         <v>583</v>
       </c>
       <c r="F139" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G139" t="s">
         <v>584</v>
       </c>
       <c r="H139">
-        <v>0.33</v>
+        <v>0.1529999971389771</v>
       </c>
       <c r="I139">
-        <v>0.33</v>
+        <v>0.5889999866485596</v>
       </c>
       <c r="J139">
-        <v>0.34</v>
+        <v>0.257999986410141</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -14203,19 +14203,19 @@
         <v>584</v>
       </c>
       <c r="F140" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G140" t="s">
         <v>584</v>
       </c>
       <c r="H140">
-        <v>0.33</v>
+        <v>0.1030000001192093</v>
       </c>
       <c r="I140">
-        <v>0.33</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="J140">
-        <v>0.34</v>
+        <v>0.4269999861717224</v>
       </c>
     </row>
     <row r="141" spans="1:10">
@@ -14235,19 +14235,19 @@
         <v>583</v>
       </c>
       <c r="F141" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G141" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H141">
-        <v>0.33</v>
+        <v>0.1289999932050705</v>
       </c>
       <c r="I141">
-        <v>0.33</v>
+        <v>0.546999990940094</v>
       </c>
       <c r="J141">
-        <v>0.34</v>
+        <v>0.3240000009536743</v>
       </c>
     </row>
     <row r="142" spans="1:10">
@@ -14267,19 +14267,19 @@
         <v>583</v>
       </c>
       <c r="F142" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G142" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H142">
-        <v>0.33</v>
+        <v>0.4289999902248383</v>
       </c>
       <c r="I142">
-        <v>0.33</v>
+        <v>0.1030000001192093</v>
       </c>
       <c r="J142">
-        <v>0.34</v>
+        <v>0.4679999947547913</v>
       </c>
     </row>
     <row r="143" spans="1:10">
@@ -14299,19 +14299,19 @@
         <v>583</v>
       </c>
       <c r="F143" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G143" t="s">
         <v>584</v>
       </c>
       <c r="H143">
-        <v>0.33</v>
+        <v>0.07999999821186066</v>
       </c>
       <c r="I143">
-        <v>0.33</v>
+        <v>0.550000011920929</v>
       </c>
       <c r="J143">
-        <v>0.34</v>
+        <v>0.3709999918937683</v>
       </c>
     </row>
     <row r="144" spans="1:10">
@@ -14331,19 +14331,19 @@
         <v>583</v>
       </c>
       <c r="F144" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G144" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H144">
-        <v>0.33</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="I144">
-        <v>0.33</v>
+        <v>0.2619999945163727</v>
       </c>
       <c r="J144">
-        <v>0.34</v>
+        <v>0.6380000114440918</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -14363,19 +14363,19 @@
         <v>584</v>
       </c>
       <c r="F145" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G145" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H145">
-        <v>0.33</v>
+        <v>0.1270000040531158</v>
       </c>
       <c r="I145">
-        <v>0.33</v>
+        <v>0.4120000004768372</v>
       </c>
       <c r="J145">
-        <v>0.34</v>
+        <v>0.460999995470047</v>
       </c>
     </row>
     <row r="146" spans="1:10">
@@ -14395,19 +14395,19 @@
         <v>584</v>
       </c>
       <c r="F146" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G146" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H146">
-        <v>0.33</v>
+        <v>0.119999997317791</v>
       </c>
       <c r="I146">
-        <v>0.33</v>
+        <v>0.1879999935626984</v>
       </c>
       <c r="J146">
-        <v>0.34</v>
+        <v>0.6919999718666077</v>
       </c>
     </row>
     <row r="147" spans="1:10">
@@ -14427,19 +14427,19 @@
         <v>583</v>
       </c>
       <c r="F147" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G147" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H147">
-        <v>0.33</v>
+        <v>0.1260000020265579</v>
       </c>
       <c r="I147">
-        <v>0.33</v>
+        <v>0.5580000281333923</v>
       </c>
       <c r="J147">
-        <v>0.34</v>
+        <v>0.3170000016689301</v>
       </c>
     </row>
     <row r="148" spans="1:10">
@@ -14459,19 +14459,19 @@
         <v>584</v>
       </c>
       <c r="F148" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G148" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H148">
-        <v>0.33</v>
+        <v>0.1270000040531158</v>
       </c>
       <c r="I148">
-        <v>0.33</v>
+        <v>0.4589999914169312</v>
       </c>
       <c r="J148">
-        <v>0.34</v>
+        <v>0.414000004529953</v>
       </c>
     </row>
     <row r="149" spans="1:10">
@@ -14491,19 +14491,19 @@
         <v>583</v>
       </c>
       <c r="F149" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G149" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H149">
-        <v>0.33</v>
+        <v>0.1220000013709068</v>
       </c>
       <c r="I149">
-        <v>0.33</v>
+        <v>0.3100000023841858</v>
       </c>
       <c r="J149">
-        <v>0.34</v>
+        <v>0.5680000185966492</v>
       </c>
     </row>
     <row r="150" spans="1:10">
@@ -14523,19 +14523,19 @@
         <v>583</v>
       </c>
       <c r="F150" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G150" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H150">
-        <v>0.33</v>
+        <v>0.06800000369548798</v>
       </c>
       <c r="I150">
-        <v>0.33</v>
+        <v>0.4169999957084656</v>
       </c>
       <c r="J150">
-        <v>0.34</v>
+        <v>0.5149999856948853</v>
       </c>
     </row>
     <row r="151" spans="1:10">
@@ -14555,19 +14555,19 @@
         <v>584</v>
       </c>
       <c r="F151" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G151" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H151">
-        <v>0.33</v>
+        <v>0.1870000064373016</v>
       </c>
       <c r="I151">
-        <v>0.33</v>
+        <v>0.3840000033378601</v>
       </c>
       <c r="J151">
-        <v>0.34</v>
+        <v>0.4289999902248383</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -14587,19 +14587,19 @@
         <v>583</v>
       </c>
       <c r="F152" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G152" t="s">
         <v>584</v>
       </c>
       <c r="H152">
-        <v>0.33</v>
+        <v>0.101000003516674</v>
       </c>
       <c r="I152">
-        <v>0.33</v>
+        <v>0.5009999871253967</v>
       </c>
       <c r="J152">
-        <v>0.34</v>
+        <v>0.3980000019073486</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -14619,19 +14619,19 @@
         <v>583</v>
       </c>
       <c r="F153" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G153" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H153">
-        <v>0.33</v>
+        <v>0.08399999886751175</v>
       </c>
       <c r="I153">
-        <v>0.33</v>
+        <v>0.515999972820282</v>
       </c>
       <c r="J153">
-        <v>0.34</v>
+        <v>0.4000000059604645</v>
       </c>
     </row>
     <row r="154" spans="1:10">
@@ -14651,19 +14651,19 @@
         <v>583</v>
       </c>
       <c r="F154" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G154" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H154">
-        <v>0.33</v>
+        <v>0.1140000000596046</v>
       </c>
       <c r="I154">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="J154">
-        <v>0.34</v>
+        <v>0.3869999945163727</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -14683,19 +14683,19 @@
         <v>583</v>
       </c>
       <c r="F155" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G155" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H155">
-        <v>0.33</v>
+        <v>0.1400000005960464</v>
       </c>
       <c r="I155">
-        <v>0.33</v>
+        <v>0.625</v>
       </c>
       <c r="J155">
-        <v>0.34</v>
+        <v>0.2339999973773956</v>
       </c>
     </row>
     <row r="156" spans="1:10">
@@ -14715,19 +14715,19 @@
         <v>584</v>
       </c>
       <c r="F156" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G156" t="s">
         <v>584</v>
       </c>
       <c r="H156">
-        <v>0.33</v>
+        <v>0.09300000220537186</v>
       </c>
       <c r="I156">
-        <v>0.33</v>
+        <v>0.4679999947547913</v>
       </c>
       <c r="J156">
-        <v>0.34</v>
+        <v>0.4390000104904175</v>
       </c>
     </row>
     <row r="157" spans="1:10">
@@ -14747,19 +14747,19 @@
         <v>583</v>
       </c>
       <c r="F157" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G157" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H157">
-        <v>0.33</v>
+        <v>0.1580000072717667</v>
       </c>
       <c r="I157">
-        <v>0.33</v>
+        <v>0.6389999985694885</v>
       </c>
       <c r="J157">
-        <v>0.34</v>
+        <v>0.2029999941587448</v>
       </c>
     </row>
     <row r="158" spans="1:10">
@@ -14779,19 +14779,19 @@
         <v>583</v>
       </c>
       <c r="F158" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G158" t="s">
         <v>584</v>
       </c>
       <c r="H158">
-        <v>0.33</v>
+        <v>0.1780000030994415</v>
       </c>
       <c r="I158">
-        <v>0.33</v>
+        <v>0.3840000033378601</v>
       </c>
       <c r="J158">
-        <v>0.34</v>
+        <v>0.4379999935626984</v>
       </c>
     </row>
     <row r="159" spans="1:10">
@@ -14811,19 +14811,19 @@
         <v>583</v>
       </c>
       <c r="F159" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G159" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H159">
-        <v>0.33</v>
+        <v>0.1299999952316284</v>
       </c>
       <c r="I159">
-        <v>0.33</v>
+        <v>0.3429999947547913</v>
       </c>
       <c r="J159">
-        <v>0.34</v>
+        <v>0.5270000100135803</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -14843,19 +14843,19 @@
         <v>584</v>
       </c>
       <c r="F160" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G160" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H160">
-        <v>0.33</v>
+        <v>0.2119999974966049</v>
       </c>
       <c r="I160">
-        <v>0.33</v>
+        <v>0.2349999994039536</v>
       </c>
       <c r="J160">
-        <v>0.34</v>
+        <v>0.5529999732971191</v>
       </c>
     </row>
     <row r="161" spans="1:10">
@@ -14875,19 +14875,19 @@
         <v>583</v>
       </c>
       <c r="F161" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G161" t="s">
         <v>584</v>
       </c>
       <c r="H161">
-        <v>0.33</v>
+        <v>0.1809999942779541</v>
       </c>
       <c r="I161">
-        <v>0.33</v>
+        <v>0.4169999957084656</v>
       </c>
       <c r="J161">
-        <v>0.34</v>
+        <v>0.4020000100135803</v>
       </c>
     </row>
     <row r="162" spans="1:10">
@@ -14907,19 +14907,19 @@
         <v>584</v>
       </c>
       <c r="F162" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G162" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H162">
-        <v>0.33</v>
+        <v>0.101000003516674</v>
       </c>
       <c r="I162">
-        <v>0.33</v>
+        <v>0.4329999983310699</v>
       </c>
       <c r="J162">
-        <v>0.34</v>
+        <v>0.4659999907016754</v>
       </c>
     </row>
     <row r="163" spans="1:10">
@@ -14936,19 +14936,19 @@
         <v>584</v>
       </c>
       <c r="F163" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G163" t="s">
         <v>584</v>
       </c>
       <c r="H163">
-        <v>0.33</v>
+        <v>0.1589999943971634</v>
       </c>
       <c r="I163">
-        <v>0.33</v>
+        <v>0.625</v>
       </c>
       <c r="J163">
-        <v>0.34</v>
+        <v>0.2160000056028366</v>
       </c>
     </row>
     <row r="164" spans="1:10">
@@ -14968,19 +14968,19 @@
         <v>584</v>
       </c>
       <c r="F164" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G164" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H164">
-        <v>0.33</v>
+        <v>0.153999999165535</v>
       </c>
       <c r="I164">
-        <v>0.33</v>
+        <v>0.4850000143051147</v>
       </c>
       <c r="J164">
-        <v>0.34</v>
+        <v>0.3610000014305115</v>
       </c>
     </row>
     <row r="165" spans="1:10">
@@ -15000,19 +15000,19 @@
         <v>583</v>
       </c>
       <c r="F165" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G165" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H165">
-        <v>0.33</v>
+        <v>0.1780000030994415</v>
       </c>
       <c r="I165">
-        <v>0.33</v>
+        <v>0.3160000145435333</v>
       </c>
       <c r="J165">
-        <v>0.34</v>
+        <v>0.5070000290870667</v>
       </c>
     </row>
     <row r="166" spans="1:10">
@@ -15032,19 +15032,19 @@
         <v>583</v>
       </c>
       <c r="F166" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G166" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H166">
-        <v>0.33</v>
+        <v>0.1369999945163727</v>
       </c>
       <c r="I166">
-        <v>0.33</v>
+        <v>0.2820000052452087</v>
       </c>
       <c r="J166">
-        <v>0.34</v>
+        <v>0.5799999833106995</v>
       </c>
     </row>
     <row r="167" spans="1:10">
@@ -15064,19 +15064,19 @@
         <v>584</v>
       </c>
       <c r="F167" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G167" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H167">
-        <v>0.33</v>
+        <v>0.1459999978542328</v>
       </c>
       <c r="I167">
-        <v>0.33</v>
+        <v>0.6389999985694885</v>
       </c>
       <c r="J167">
-        <v>0.34</v>
+        <v>0.2150000035762787</v>
       </c>
     </row>
     <row r="168" spans="1:10">
@@ -15096,19 +15096,19 @@
         <v>584</v>
       </c>
       <c r="F168" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G168" t="s">
         <v>584</v>
       </c>
       <c r="H168">
-        <v>0.33</v>
+        <v>0.2680000066757202</v>
       </c>
       <c r="I168">
-        <v>0.33</v>
+        <v>0.4850000143051147</v>
       </c>
       <c r="J168">
-        <v>0.34</v>
+        <v>0.2469999939203262</v>
       </c>
     </row>
     <row r="169" spans="1:10">
@@ -15128,19 +15128,19 @@
         <v>583</v>
       </c>
       <c r="F169" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G169" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H169">
-        <v>0.33</v>
+        <v>0.07800000160932541</v>
       </c>
       <c r="I169">
-        <v>0.33</v>
+        <v>0.3889999985694885</v>
       </c>
       <c r="J169">
-        <v>0.34</v>
+        <v>0.5329999923706055</v>
       </c>
     </row>
     <row r="170" spans="1:10">
@@ -15160,19 +15160,19 @@
         <v>583</v>
       </c>
       <c r="F170" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G170" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H170">
-        <v>0.33</v>
+        <v>0.0820000022649765</v>
       </c>
       <c r="I170">
-        <v>0.33</v>
+        <v>0.4460000097751617</v>
       </c>
       <c r="J170">
-        <v>0.34</v>
+        <v>0.4720000028610229</v>
       </c>
     </row>
     <row r="171" spans="1:10">
@@ -15192,19 +15192,19 @@
         <v>584</v>
       </c>
       <c r="F171" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G171" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H171">
-        <v>0.33</v>
+        <v>0.1030000001192093</v>
       </c>
       <c r="I171">
-        <v>0.33</v>
+        <v>0.4909999966621399</v>
       </c>
       <c r="J171">
-        <v>0.34</v>
+        <v>0.4059999883174896</v>
       </c>
     </row>
     <row r="172" spans="1:10">
@@ -15224,19 +15224,19 @@
         <v>583</v>
       </c>
       <c r="F172" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G172" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H172">
-        <v>0.33</v>
+        <v>0.09200000017881393</v>
       </c>
       <c r="I172">
-        <v>0.33</v>
+        <v>0.3959999978542328</v>
       </c>
       <c r="J172">
-        <v>0.34</v>
+        <v>0.5120000243186951</v>
       </c>
     </row>
     <row r="173" spans="1:10">
@@ -15256,19 +15256,19 @@
         <v>584</v>
       </c>
       <c r="F173" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G173" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H173">
-        <v>0.33</v>
+        <v>0.07500000298023224</v>
       </c>
       <c r="I173">
-        <v>0.33</v>
+        <v>0.6549999713897705</v>
       </c>
       <c r="J173">
-        <v>0.34</v>
+        <v>0.2700000107288361</v>
       </c>
     </row>
     <row r="174" spans="1:10">
@@ -15288,19 +15288,19 @@
         <v>584</v>
       </c>
       <c r="F174" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G174" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H174">
-        <v>0.33</v>
+        <v>0.1870000064373016</v>
       </c>
       <c r="I174">
-        <v>0.33</v>
+        <v>0.2809999883174896</v>
       </c>
       <c r="J174">
-        <v>0.34</v>
+        <v>0.531000018119812</v>
       </c>
     </row>
     <row r="175" spans="1:10">
@@ -15320,19 +15320,19 @@
         <v>583</v>
       </c>
       <c r="F175" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G175" t="s">
         <v>584</v>
       </c>
       <c r="H175">
-        <v>0.33</v>
+        <v>0.2820000052452087</v>
       </c>
       <c r="I175">
-        <v>0.33</v>
+        <v>0.4629999995231628</v>
       </c>
       <c r="J175">
-        <v>0.34</v>
+        <v>0.2549999952316284</v>
       </c>
     </row>
     <row r="176" spans="1:10">
@@ -15352,19 +15352,19 @@
         <v>584</v>
       </c>
       <c r="F176" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G176" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H176">
-        <v>0.33</v>
+        <v>0.1870000064373016</v>
       </c>
       <c r="I176">
-        <v>0.33</v>
+        <v>0.3230000138282776</v>
       </c>
       <c r="J176">
-        <v>0.34</v>
+        <v>0.4900000095367432</v>
       </c>
     </row>
     <row r="177" spans="1:10">
@@ -15384,19 +15384,19 @@
         <v>583</v>
       </c>
       <c r="F177" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G177" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H177">
-        <v>0.33</v>
+        <v>0.2049999982118607</v>
       </c>
       <c r="I177">
-        <v>0.33</v>
+        <v>0.5299999713897705</v>
       </c>
       <c r="J177">
-        <v>0.34</v>
+        <v>0.2649999856948853</v>
       </c>
     </row>
     <row r="178" spans="1:10">
@@ -15416,19 +15416,19 @@
         <v>583</v>
       </c>
       <c r="F178" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G178" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H178">
-        <v>0.33</v>
+        <v>0.1169999986886978</v>
       </c>
       <c r="I178">
-        <v>0.33</v>
+        <v>0.3880000114440918</v>
       </c>
       <c r="J178">
-        <v>0.34</v>
+        <v>0.4959999918937683</v>
       </c>
     </row>
     <row r="179" spans="1:10">
@@ -15448,19 +15448,19 @@
         <v>583</v>
       </c>
       <c r="F179" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G179" t="s">
         <v>584</v>
       </c>
       <c r="H179">
-        <v>0.33</v>
+        <v>0.2000000029802322</v>
       </c>
       <c r="I179">
-        <v>0.33</v>
+        <v>0.4959999918937683</v>
       </c>
       <c r="J179">
-        <v>0.34</v>
+        <v>0.3030000030994415</v>
       </c>
     </row>
     <row r="180" spans="1:10">
@@ -15480,19 +15480,19 @@
         <v>583</v>
       </c>
       <c r="F180" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G180" t="s">
         <v>584</v>
       </c>
       <c r="H180">
-        <v>0.33</v>
+        <v>0.09300000220537186</v>
       </c>
       <c r="I180">
-        <v>0.33</v>
+        <v>0.4720000028610229</v>
       </c>
       <c r="J180">
-        <v>0.34</v>
+        <v>0.4350000023841858</v>
       </c>
     </row>
     <row r="181" spans="1:10">
@@ -15512,19 +15512,19 @@
         <v>583</v>
       </c>
       <c r="F181" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G181" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H181">
-        <v>0.33</v>
+        <v>0.1129999980330467</v>
       </c>
       <c r="I181">
-        <v>0.33</v>
+        <v>0.2010000050067902</v>
       </c>
       <c r="J181">
-        <v>0.34</v>
+        <v>0.6859999895095825</v>
       </c>
     </row>
     <row r="182" spans="1:10">
@@ -15544,19 +15544,19 @@
         <v>584</v>
       </c>
       <c r="F182" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G182" t="s">
         <v>584</v>
       </c>
       <c r="H182">
-        <v>0.33</v>
+        <v>0.210999995470047</v>
       </c>
       <c r="I182">
-        <v>0.33</v>
+        <v>0.5220000147819519</v>
       </c>
       <c r="J182">
-        <v>0.34</v>
+        <v>0.2680000066757202</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -15576,19 +15576,19 @@
         <v>583</v>
       </c>
       <c r="F183" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G183" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H183">
-        <v>0.33</v>
+        <v>0.07599999755620956</v>
       </c>
       <c r="I183">
-        <v>0.33</v>
+        <v>0.656000018119812</v>
       </c>
       <c r="J183">
-        <v>0.34</v>
+        <v>0.2669999897480011</v>
       </c>
     </row>
     <row r="184" spans="1:10">
@@ -15608,19 +15608,19 @@
         <v>584</v>
       </c>
       <c r="F184" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G184" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H184">
-        <v>0.33</v>
+        <v>0.1030000001192093</v>
       </c>
       <c r="I184">
-        <v>0.33</v>
+        <v>0.4519999921321869</v>
       </c>
       <c r="J184">
-        <v>0.34</v>
+        <v>0.4449999928474426</v>
       </c>
     </row>
     <row r="185" spans="1:10">
@@ -15640,19 +15640,19 @@
         <v>583</v>
       </c>
       <c r="F185" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G185" t="s">
         <v>584</v>
       </c>
       <c r="H185">
-        <v>0.33</v>
+        <v>0.1340000033378601</v>
       </c>
       <c r="I185">
-        <v>0.33</v>
+        <v>0.3050000071525574</v>
       </c>
       <c r="J185">
-        <v>0.34</v>
+        <v>0.5609999895095825</v>
       </c>
     </row>
     <row r="186" spans="1:10">
@@ -15672,19 +15672,19 @@
         <v>583</v>
       </c>
       <c r="F186" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G186" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H186">
-        <v>0.33</v>
+        <v>0.1469999998807907</v>
       </c>
       <c r="I186">
-        <v>0.33</v>
+        <v>0.4709999859333038</v>
       </c>
       <c r="J186">
-        <v>0.34</v>
+        <v>0.3810000121593475</v>
       </c>
     </row>
     <row r="187" spans="1:10">
@@ -15704,19 +15704,19 @@
         <v>584</v>
       </c>
       <c r="F187" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G187" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H187">
-        <v>0.33</v>
+        <v>0.1190000027418137</v>
       </c>
       <c r="I187">
-        <v>0.33</v>
+        <v>0.6100000143051147</v>
       </c>
       <c r="J187">
-        <v>0.34</v>
+        <v>0.2709999978542328</v>
       </c>
     </row>
     <row r="188" spans="1:10">
@@ -15736,19 +15736,19 @@
         <v>584</v>
       </c>
       <c r="F188" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G188" t="s">
         <v>584</v>
       </c>
       <c r="H188">
-        <v>0.33</v>
+        <v>0.1230000033974648</v>
       </c>
       <c r="I188">
-        <v>0.33</v>
+        <v>0.4000000059604645</v>
       </c>
       <c r="J188">
-        <v>0.34</v>
+        <v>0.4769999980926514</v>
       </c>
     </row>
     <row r="189" spans="1:10">
@@ -15768,19 +15768,19 @@
         <v>584</v>
       </c>
       <c r="F189" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G189" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H189">
-        <v>0.33</v>
+        <v>0.07800000160932541</v>
       </c>
       <c r="I189">
-        <v>0.33</v>
+        <v>0.5519999861717224</v>
       </c>
       <c r="J189">
-        <v>0.34</v>
+        <v>0.3709999918937683</v>
       </c>
     </row>
     <row r="190" spans="1:10">
@@ -15800,19 +15800,19 @@
         <v>584</v>
       </c>
       <c r="F190" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G190" t="s">
         <v>584</v>
       </c>
       <c r="H190">
-        <v>0.33</v>
+        <v>0.1749999970197678</v>
       </c>
       <c r="I190">
-        <v>0.33</v>
+        <v>0.4839999973773956</v>
       </c>
       <c r="J190">
-        <v>0.34</v>
+        <v>0.3409999907016754</v>
       </c>
     </row>
     <row r="191" spans="1:10">
@@ -15832,19 +15832,19 @@
         <v>583</v>
       </c>
       <c r="F191" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G191" t="s">
         <v>584</v>
       </c>
       <c r="H191">
-        <v>0.33</v>
+        <v>0.08799999952316284</v>
       </c>
       <c r="I191">
-        <v>0.33</v>
+        <v>0.5090000033378601</v>
       </c>
       <c r="J191">
-        <v>0.34</v>
+        <v>0.4029999971389771</v>
       </c>
     </row>
     <row r="192" spans="1:10">
@@ -15864,19 +15864,19 @@
         <v>583</v>
       </c>
       <c r="F192" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G192" t="s">
         <v>584</v>
       </c>
       <c r="H192">
-        <v>0.33</v>
+        <v>0.09700000286102295</v>
       </c>
       <c r="I192">
-        <v>0.33</v>
+        <v>0.5630000233650208</v>
       </c>
       <c r="J192">
-        <v>0.34</v>
+        <v>0.3409999907016754</v>
       </c>
     </row>
     <row r="193" spans="1:10">
@@ -15896,19 +15896,19 @@
         <v>583</v>
       </c>
       <c r="F193" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G193" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H193">
-        <v>0.33</v>
+        <v>0.07800000160932541</v>
       </c>
       <c r="I193">
-        <v>0.33</v>
+        <v>0.4850000143051147</v>
       </c>
       <c r="J193">
-        <v>0.34</v>
+        <v>0.4370000064373016</v>
       </c>
     </row>
     <row r="194" spans="1:10">
@@ -15925,19 +15925,19 @@
         <v>584</v>
       </c>
       <c r="F194" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G194" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H194">
-        <v>0.33</v>
+        <v>0.07400000095367432</v>
       </c>
       <c r="I194">
-        <v>0.33</v>
+        <v>0.6259999871253967</v>
       </c>
       <c r="J194">
-        <v>0.34</v>
+        <v>0.300000011920929</v>
       </c>
     </row>
     <row r="195" spans="1:10">
@@ -15957,19 +15957,19 @@
         <v>583</v>
       </c>
       <c r="F195" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G195" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H195">
-        <v>0.33</v>
+        <v>0.1609999984502792</v>
       </c>
       <c r="I195">
-        <v>0.33</v>
+        <v>0.4429999887943268</v>
       </c>
       <c r="J195">
-        <v>0.34</v>
+        <v>0.3959999978542328</v>
       </c>
     </row>
     <row r="196" spans="1:10">
@@ -15989,19 +15989,19 @@
         <v>583</v>
       </c>
       <c r="F196" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G196" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H196">
-        <v>0.33</v>
+        <v>0.1459999978542328</v>
       </c>
       <c r="I196">
-        <v>0.33</v>
+        <v>0.4079999923706055</v>
       </c>
       <c r="J196">
-        <v>0.34</v>
+        <v>0.4460000097751617</v>
       </c>
     </row>
     <row r="197" spans="1:10">
@@ -16021,19 +16021,19 @@
         <v>583</v>
       </c>
       <c r="F197" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G197" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H197">
-        <v>0.33</v>
+        <v>0.3429999947547913</v>
       </c>
       <c r="I197">
-        <v>0.33</v>
+        <v>0.2590000033378601</v>
       </c>
       <c r="J197">
-        <v>0.34</v>
+        <v>0.3970000147819519</v>
       </c>
     </row>
     <row r="198" spans="1:10">
@@ -16053,19 +16053,19 @@
         <v>583</v>
       </c>
       <c r="F198" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G198" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H198">
-        <v>0.33</v>
+        <v>0.324999988079071</v>
       </c>
       <c r="I198">
-        <v>0.33</v>
+        <v>0.1809999942779541</v>
       </c>
       <c r="J198">
-        <v>0.34</v>
+        <v>0.4939999878406525</v>
       </c>
     </row>
     <row r="199" spans="1:10">
@@ -16085,19 +16085,19 @@
         <v>583</v>
       </c>
       <c r="F199" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G199" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H199">
-        <v>0.33</v>
+        <v>0.1570000052452087</v>
       </c>
       <c r="I199">
-        <v>0.33</v>
+        <v>0.2960000038146973</v>
       </c>
       <c r="J199">
-        <v>0.34</v>
+        <v>0.546999990940094</v>
       </c>
     </row>
     <row r="200" spans="1:10">
@@ -16117,19 +16117,19 @@
         <v>583</v>
       </c>
       <c r="F200" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G200" t="s">
         <v>584</v>
       </c>
       <c r="H200">
-        <v>0.33</v>
+        <v>0.1209999993443489</v>
       </c>
       <c r="I200">
-        <v>0.33</v>
+        <v>0.2989999949932098</v>
       </c>
       <c r="J200">
-        <v>0.34</v>
+        <v>0.5799999833106995</v>
       </c>
     </row>
     <row r="201" spans="1:10">
@@ -16149,19 +16149,19 @@
         <v>583</v>
       </c>
       <c r="F201" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G201" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H201">
-        <v>0.33</v>
+        <v>0.1480000019073486</v>
       </c>
       <c r="I201">
-        <v>0.33</v>
+        <v>0.5049999952316284</v>
       </c>
       <c r="J201">
-        <v>0.34</v>
+        <v>0.3470000028610229</v>
       </c>
     </row>
     <row r="202" spans="1:10">
@@ -16181,19 +16181,19 @@
         <v>584</v>
       </c>
       <c r="F202" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G202" t="s">
         <v>584</v>
       </c>
       <c r="H202">
-        <v>0.33</v>
+        <v>0.119999997317791</v>
       </c>
       <c r="I202">
-        <v>0.33</v>
+        <v>0.453000009059906</v>
       </c>
       <c r="J202">
-        <v>0.34</v>
+        <v>0.4269999861717224</v>
       </c>
     </row>
     <row r="203" spans="1:10">
@@ -16213,19 +16213,19 @@
         <v>583</v>
       </c>
       <c r="F203" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G203" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H203">
-        <v>0.33</v>
+        <v>0.0949999988079071</v>
       </c>
       <c r="I203">
-        <v>0.33</v>
+        <v>0.4690000116825104</v>
       </c>
       <c r="J203">
-        <v>0.34</v>
+        <v>0.4359999895095825</v>
       </c>
     </row>
     <row r="204" spans="1:10">
@@ -16245,19 +16245,19 @@
         <v>583</v>
       </c>
       <c r="F204" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G204" t="s">
         <v>584</v>
       </c>
       <c r="H204">
-        <v>0.33</v>
+        <v>0.07599999755620956</v>
       </c>
       <c r="I204">
-        <v>0.33</v>
+        <v>0.5820000171661377</v>
       </c>
       <c r="J204">
-        <v>0.34</v>
+        <v>0.3420000076293945</v>
       </c>
     </row>
     <row r="205" spans="1:10">
@@ -16277,19 +16277,19 @@
         <v>583</v>
       </c>
       <c r="F205" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G205" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H205">
-        <v>0.33</v>
+        <v>0.08799999952316284</v>
       </c>
       <c r="I205">
-        <v>0.33</v>
+        <v>0.2020000070333481</v>
       </c>
       <c r="J205">
-        <v>0.34</v>
+        <v>0.7099999785423279</v>
       </c>
     </row>
     <row r="206" spans="1:10">
@@ -16309,19 +16309,19 @@
         <v>584</v>
       </c>
       <c r="F206" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G206" t="s">
         <v>584</v>
       </c>
       <c r="H206">
-        <v>0.33</v>
+        <v>0.08900000154972076</v>
       </c>
       <c r="I206">
-        <v>0.33</v>
+        <v>0.2080000042915344</v>
       </c>
       <c r="J206">
-        <v>0.34</v>
+        <v>0.7039999961853027</v>
       </c>
     </row>
     <row r="207" spans="1:10">
@@ -16341,19 +16341,19 @@
         <v>583</v>
       </c>
       <c r="F207" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G207" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H207">
-        <v>0.33</v>
+        <v>0.1169999986886978</v>
       </c>
       <c r="I207">
-        <v>0.33</v>
+        <v>0.3740000128746033</v>
       </c>
       <c r="J207">
-        <v>0.34</v>
+        <v>0.5090000033378601</v>
       </c>
     </row>
     <row r="208" spans="1:10">
@@ -16373,19 +16373,19 @@
         <v>584</v>
       </c>
       <c r="F208" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G208" t="s">
         <v>584</v>
       </c>
       <c r="H208">
-        <v>0.33</v>
+        <v>0.07400000095367432</v>
       </c>
       <c r="I208">
-        <v>0.33</v>
+        <v>0.6430000066757202</v>
       </c>
       <c r="J208">
-        <v>0.34</v>
+        <v>0.2829999923706055</v>
       </c>
     </row>
     <row r="209" spans="1:10">
@@ -16405,19 +16405,19 @@
         <v>583</v>
       </c>
       <c r="F209" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G209" t="s">
         <v>584</v>
       </c>
       <c r="H209">
-        <v>0.33</v>
+        <v>0.07699999958276749</v>
       </c>
       <c r="I209">
-        <v>0.33</v>
+        <v>0.5809999704360962</v>
       </c>
       <c r="J209">
-        <v>0.34</v>
+        <v>0.3420000076293945</v>
       </c>
     </row>
     <row r="210" spans="1:10">
@@ -16437,19 +16437,19 @@
         <v>584</v>
       </c>
       <c r="F210" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G210" t="s">
         <v>584</v>
       </c>
       <c r="H210">
-        <v>0.33</v>
+        <v>0.181999996304512</v>
       </c>
       <c r="I210">
-        <v>0.33</v>
+        <v>0.5740000009536743</v>
       </c>
       <c r="J210">
-        <v>0.34</v>
+        <v>0.2440000027418137</v>
       </c>
     </row>
     <row r="211" spans="1:10">
@@ -16469,19 +16469,19 @@
         <v>583</v>
       </c>
       <c r="F211" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G211" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H211">
-        <v>0.33</v>
+        <v>0.1940000057220459</v>
       </c>
       <c r="I211">
-        <v>0.33</v>
+        <v>0.3050000071525574</v>
       </c>
       <c r="J211">
-        <v>0.34</v>
+        <v>0.5009999871253967</v>
       </c>
     </row>
     <row r="212" spans="1:10">
@@ -16501,19 +16501,19 @@
         <v>584</v>
       </c>
       <c r="F212" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G212" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H212">
-        <v>0.33</v>
+        <v>0.1669999957084656</v>
       </c>
       <c r="I212">
-        <v>0.33</v>
+        <v>0.6000000238418579</v>
       </c>
       <c r="J212">
-        <v>0.34</v>
+        <v>0.2329999953508377</v>
       </c>
     </row>
     <row r="213" spans="1:10">
@@ -16533,19 +16533,19 @@
         <v>584</v>
       </c>
       <c r="F213" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G213" t="s">
         <v>584</v>
       </c>
       <c r="H213">
-        <v>0.33</v>
+        <v>0.08900000154972076</v>
       </c>
       <c r="I213">
-        <v>0.33</v>
+        <v>0.628000020980835</v>
       </c>
       <c r="J213">
-        <v>0.34</v>
+        <v>0.2829999923706055</v>
       </c>
     </row>
     <row r="214" spans="1:10">
@@ -16565,19 +16565,19 @@
         <v>584</v>
       </c>
       <c r="F214" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G214" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H214">
-        <v>0.33</v>
+        <v>0.1500000059604645</v>
       </c>
       <c r="I214">
-        <v>0.33</v>
+        <v>0.4860000014305115</v>
       </c>
       <c r="J214">
-        <v>0.34</v>
+        <v>0.363999992609024</v>
       </c>
     </row>
     <row r="215" spans="1:10">
@@ -16597,19 +16597,19 @@
         <v>584</v>
       </c>
       <c r="F215" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G215" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H215">
-        <v>0.33</v>
+        <v>0.2240000069141388</v>
       </c>
       <c r="I215">
-        <v>0.33</v>
+        <v>0.5590000152587891</v>
       </c>
       <c r="J215">
-        <v>0.34</v>
+        <v>0.2160000056028366</v>
       </c>
     </row>
     <row r="216" spans="1:10">
@@ -16629,19 +16629,19 @@
         <v>584</v>
       </c>
       <c r="F216" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G216" t="s">
         <v>584</v>
       </c>
       <c r="H216">
-        <v>0.33</v>
+        <v>0.1400000005960464</v>
       </c>
       <c r="I216">
-        <v>0.33</v>
+        <v>0.4000000059604645</v>
       </c>
       <c r="J216">
-        <v>0.34</v>
+        <v>0.4589999914169312</v>
       </c>
     </row>
     <row r="217" spans="1:10">
@@ -16661,19 +16661,19 @@
         <v>583</v>
       </c>
       <c r="F217" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G217" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H217">
-        <v>0.33</v>
+        <v>0.07500000298023224</v>
       </c>
       <c r="I217">
-        <v>0.33</v>
+        <v>0.6610000133514404</v>
       </c>
       <c r="J217">
-        <v>0.34</v>
+        <v>0.2639999985694885</v>
       </c>
     </row>
     <row r="218" spans="1:10">
@@ -16693,19 +16693,19 @@
         <v>583</v>
       </c>
       <c r="F218" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G218" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H218">
-        <v>0.33</v>
+        <v>0.1630000025033951</v>
       </c>
       <c r="I218">
-        <v>0.33</v>
+        <v>0.2540000081062317</v>
       </c>
       <c r="J218">
-        <v>0.34</v>
+        <v>0.5830000042915344</v>
       </c>
     </row>
     <row r="219" spans="1:10">
@@ -16725,19 +16725,19 @@
         <v>584</v>
       </c>
       <c r="F219" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G219" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H219">
-        <v>0.33</v>
+        <v>0.1469999998807907</v>
       </c>
       <c r="I219">
-        <v>0.33</v>
+        <v>0.4239999949932098</v>
       </c>
       <c r="J219">
-        <v>0.34</v>
+        <v>0.4289999902248383</v>
       </c>
     </row>
     <row r="220" spans="1:10">
@@ -16757,19 +16757,19 @@
         <v>583</v>
       </c>
       <c r="F220" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G220" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H220">
-        <v>0.33</v>
+        <v>0.08399999886751175</v>
       </c>
       <c r="I220">
-        <v>0.33</v>
+        <v>0.4519999921321869</v>
       </c>
       <c r="J220">
-        <v>0.34</v>
+        <v>0.4639999866485596</v>
       </c>
     </row>
     <row r="221" spans="1:10">
@@ -16786,19 +16786,19 @@
         <v>584</v>
       </c>
       <c r="F221" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G221" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H221">
-        <v>0.33</v>
+        <v>0.1410000026226044</v>
       </c>
       <c r="I221">
-        <v>0.33</v>
+        <v>0.4790000021457672</v>
       </c>
       <c r="J221">
-        <v>0.34</v>
+        <v>0.3799999952316284</v>
       </c>
     </row>
     <row r="222" spans="1:10">
@@ -16818,19 +16818,19 @@
         <v>584</v>
       </c>
       <c r="F222" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G222" t="s">
         <v>584</v>
       </c>
       <c r="H222">
-        <v>0.33</v>
+        <v>0.07199999690055847</v>
       </c>
       <c r="I222">
-        <v>0.33</v>
+        <v>0.6850000023841858</v>
       </c>
       <c r="J222">
-        <v>0.34</v>
+        <v>0.2430000007152557</v>
       </c>
     </row>
     <row r="223" spans="1:10">
@@ -16850,19 +16850,19 @@
         <v>583</v>
       </c>
       <c r="F223" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G223" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H223">
-        <v>0.33</v>
+        <v>0.1379999965429306</v>
       </c>
       <c r="I223">
-        <v>0.33</v>
+        <v>0.2339999973773956</v>
       </c>
       <c r="J223">
-        <v>0.34</v>
+        <v>0.628000020980835</v>
       </c>
     </row>
     <row r="224" spans="1:10">
@@ -16882,19 +16882,19 @@
         <v>583</v>
       </c>
       <c r="F224" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G224" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H224">
-        <v>0.33</v>
+        <v>0.1630000025033951</v>
       </c>
       <c r="I224">
-        <v>0.33</v>
+        <v>0.2479999959468842</v>
       </c>
       <c r="J224">
-        <v>0.34</v>
+        <v>0.5889999866485596</v>
       </c>
     </row>
     <row r="225" spans="1:10">
@@ -16914,19 +16914,19 @@
         <v>583</v>
       </c>
       <c r="F225" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G225" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H225">
-        <v>0.33</v>
+        <v>0.2179999947547913</v>
       </c>
       <c r="I225">
-        <v>0.33</v>
+        <v>0.3849999904632568</v>
       </c>
       <c r="J225">
-        <v>0.34</v>
+        <v>0.3970000147819519</v>
       </c>
     </row>
     <row r="226" spans="1:10">
@@ -16946,19 +16946,19 @@
         <v>583</v>
       </c>
       <c r="F226" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G226" t="s">
         <v>584</v>
       </c>
       <c r="H226">
-        <v>0.33</v>
+        <v>0.1770000010728836</v>
       </c>
       <c r="I226">
-        <v>0.33</v>
+        <v>0.5659999847412109</v>
       </c>
       <c r="J226">
-        <v>0.34</v>
+        <v>0.257999986410141</v>
       </c>
     </row>
     <row r="227" spans="1:10">
@@ -16978,19 +16978,19 @@
         <v>583</v>
       </c>
       <c r="F227" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G227" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H227">
-        <v>0.33</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="I227">
-        <v>0.33</v>
+        <v>0.3630000054836273</v>
       </c>
       <c r="J227">
-        <v>0.34</v>
+        <v>0.3569999933242798</v>
       </c>
     </row>
     <row r="228" spans="1:10">
@@ -17010,19 +17010,19 @@
         <v>583</v>
       </c>
       <c r="F228" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G228" t="s">
         <v>584</v>
       </c>
       <c r="H228">
-        <v>0.33</v>
+        <v>0.2440000027418137</v>
       </c>
       <c r="I228">
-        <v>0.33</v>
+        <v>0.2509999871253967</v>
       </c>
       <c r="J228">
-        <v>0.34</v>
+        <v>0.5040000081062317</v>
       </c>
     </row>
     <row r="229" spans="1:10">
@@ -17042,19 +17042,19 @@
         <v>583</v>
       </c>
       <c r="F229" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G229" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H229">
-        <v>0.33</v>
+        <v>0.09700000286102295</v>
       </c>
       <c r="I229">
-        <v>0.33</v>
+        <v>0.382999986410141</v>
       </c>
       <c r="J229">
-        <v>0.34</v>
+        <v>0.5199999809265137</v>
       </c>
     </row>
     <row r="230" spans="1:10">
@@ -17074,19 +17074,19 @@
         <v>583</v>
       </c>
       <c r="F230" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G230" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H230">
-        <v>0.33</v>
+        <v>0.1480000019073486</v>
       </c>
       <c r="I230">
-        <v>0.33</v>
+        <v>0.2259999960660934</v>
       </c>
       <c r="J230">
-        <v>0.34</v>
+        <v>0.6259999871253967</v>
       </c>
     </row>
     <row r="231" spans="1:10">
@@ -17106,19 +17106,19 @@
         <v>583</v>
       </c>
       <c r="F231" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G231" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H231">
-        <v>0.33</v>
+        <v>0.1519999951124191</v>
       </c>
       <c r="I231">
-        <v>0.33</v>
+        <v>0.2199999988079071</v>
       </c>
       <c r="J231">
-        <v>0.34</v>
+        <v>0.628000020980835</v>
       </c>
     </row>
     <row r="232" spans="1:10">
@@ -17138,19 +17138,19 @@
         <v>583</v>
       </c>
       <c r="F232" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G232" t="s">
         <v>584</v>
       </c>
       <c r="H232">
-        <v>0.33</v>
+        <v>0.1749999970197678</v>
       </c>
       <c r="I232">
-        <v>0.33</v>
+        <v>0.5960000157356262</v>
       </c>
       <c r="J232">
-        <v>0.34</v>
+        <v>0.2290000021457672</v>
       </c>
     </row>
     <row r="233" spans="1:10">
@@ -17170,19 +17170,19 @@
         <v>583</v>
       </c>
       <c r="F233" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G233" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H233">
-        <v>0.33</v>
+        <v>0.07800000160932541</v>
       </c>
       <c r="I233">
-        <v>0.33</v>
+        <v>0.6549999713897705</v>
       </c>
       <c r="J233">
-        <v>0.34</v>
+        <v>0.2669999897480011</v>
       </c>
     </row>
     <row r="234" spans="1:10">
@@ -17202,19 +17202,19 @@
         <v>583</v>
       </c>
       <c r="F234" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G234" t="s">
         <v>584</v>
       </c>
       <c r="H234">
-        <v>0.33</v>
+        <v>0.09799999743700027</v>
       </c>
       <c r="I234">
-        <v>0.33</v>
+        <v>0.6069999933242798</v>
       </c>
       <c r="J234">
-        <v>0.34</v>
+        <v>0.2960000038146973</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -17234,19 +17234,19 @@
         <v>584</v>
       </c>
       <c r="F235" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G235" t="s">
         <v>584</v>
       </c>
       <c r="H235">
-        <v>0.33</v>
+        <v>0.1630000025033951</v>
       </c>
       <c r="I235">
-        <v>0.33</v>
+        <v>0.449999988079071</v>
       </c>
       <c r="J235">
-        <v>0.34</v>
+        <v>0.3869999945163727</v>
       </c>
     </row>
     <row r="236" spans="1:10">
@@ -17266,19 +17266,19 @@
         <v>584</v>
       </c>
       <c r="F236" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G236" t="s">
         <v>584</v>
       </c>
       <c r="H236">
-        <v>0.33</v>
+        <v>0.1790000051259995</v>
       </c>
       <c r="I236">
-        <v>0.33</v>
+        <v>0.5910000205039978</v>
       </c>
       <c r="J236">
-        <v>0.34</v>
+        <v>0.2290000021457672</v>
       </c>
     </row>
     <row r="237" spans="1:10">
@@ -17298,19 +17298,19 @@
         <v>583</v>
       </c>
       <c r="F237" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G237" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H237">
-        <v>0.33</v>
+        <v>0.1609999984502792</v>
       </c>
       <c r="I237">
-        <v>0.33</v>
+        <v>0.4129999876022339</v>
       </c>
       <c r="J237">
-        <v>0.34</v>
+        <v>0.4259999990463257</v>
       </c>
     </row>
     <row r="238" spans="1:10">
@@ -17330,19 +17330,19 @@
         <v>583</v>
       </c>
       <c r="F238" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G238" t="s">
         <v>584</v>
       </c>
       <c r="H238">
-        <v>0.33</v>
+        <v>0.1420000046491623</v>
       </c>
       <c r="I238">
-        <v>0.33</v>
+        <v>0.593999981880188</v>
       </c>
       <c r="J238">
-        <v>0.34</v>
+        <v>0.2639999985694885</v>
       </c>
     </row>
     <row r="239" spans="1:10">
@@ -17362,19 +17362,19 @@
         <v>583</v>
       </c>
       <c r="F239" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G239" t="s">
         <v>584</v>
       </c>
       <c r="H239">
-        <v>0.33</v>
+        <v>0.09399999678134918</v>
       </c>
       <c r="I239">
-        <v>0.33</v>
+        <v>0.6269999742507935</v>
       </c>
       <c r="J239">
-        <v>0.34</v>
+        <v>0.2790000140666962</v>
       </c>
     </row>
     <row r="240" spans="1:10">
@@ -17394,19 +17394,19 @@
         <v>584</v>
       </c>
       <c r="F240" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G240" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H240">
-        <v>0.33</v>
+        <v>0.1809999942779541</v>
       </c>
       <c r="I240">
-        <v>0.33</v>
+        <v>0.2599999904632568</v>
       </c>
       <c r="J240">
-        <v>0.34</v>
+        <v>0.5590000152587891</v>
       </c>
     </row>
     <row r="241" spans="1:10">
@@ -17426,19 +17426,19 @@
         <v>584</v>
       </c>
       <c r="F241" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G241" t="s">
         <v>584</v>
       </c>
       <c r="H241">
-        <v>0.33</v>
+        <v>0.1669999957084656</v>
       </c>
       <c r="I241">
-        <v>0.33</v>
+        <v>0.5090000033378601</v>
       </c>
       <c r="J241">
-        <v>0.34</v>
+        <v>0.3230000138282776</v>
       </c>
     </row>
     <row r="242" spans="1:10">
@@ -17458,19 +17458,19 @@
         <v>583</v>
       </c>
       <c r="F242" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G242" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H242">
-        <v>0.33</v>
+        <v>0.1220000013709068</v>
       </c>
       <c r="I242">
-        <v>0.33</v>
+        <v>0.2349999994039536</v>
       </c>
       <c r="J242">
-        <v>0.34</v>
+        <v>0.6430000066757202</v>
       </c>
     </row>
     <row r="243" spans="1:10">
@@ -17496,13 +17496,13 @@
         <v>584</v>
       </c>
       <c r="H243">
-        <v>0.33</v>
+        <v>0.4510000050067902</v>
       </c>
       <c r="I243">
-        <v>0.33</v>
+        <v>0.1879999935626984</v>
       </c>
       <c r="J243">
-        <v>0.34</v>
+        <v>0.3610000014305115</v>
       </c>
     </row>
     <row r="244" spans="1:10">
@@ -17522,19 +17522,19 @@
         <v>584</v>
       </c>
       <c r="F244" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G244" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H244">
-        <v>0.33</v>
+        <v>0.1469999998807907</v>
       </c>
       <c r="I244">
-        <v>0.33</v>
+        <v>0.4869999885559082</v>
       </c>
       <c r="J244">
-        <v>0.34</v>
+        <v>0.3659999966621399</v>
       </c>
     </row>
     <row r="245" spans="1:10">
@@ -17554,19 +17554,19 @@
         <v>583</v>
       </c>
       <c r="F245" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H245">
-        <v>0.33</v>
+        <v>0.1059999987483025</v>
       </c>
       <c r="I245">
-        <v>0.33</v>
+        <v>0.4480000138282776</v>
       </c>
       <c r="J245">
-        <v>0.34</v>
+        <v>0.4460000097751617</v>
       </c>
     </row>
     <row r="246" spans="1:10">
@@ -17586,19 +17586,19 @@
         <v>584</v>
       </c>
       <c r="F246" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G246" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H246">
-        <v>0.33</v>
+        <v>0.2300000041723251</v>
       </c>
       <c r="I246">
-        <v>0.33</v>
+        <v>0.4659999907016754</v>
       </c>
       <c r="J246">
-        <v>0.34</v>
+        <v>0.3039999902248383</v>
       </c>
     </row>
     <row r="247" spans="1:10">
@@ -17618,19 +17618,19 @@
         <v>583</v>
       </c>
       <c r="F247" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G247" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H247">
-        <v>0.33</v>
+        <v>0.136000007390976</v>
       </c>
       <c r="I247">
-        <v>0.33</v>
+        <v>0.4659999907016754</v>
       </c>
       <c r="J247">
-        <v>0.34</v>
+        <v>0.3989999890327454</v>
       </c>
     </row>
     <row r="248" spans="1:10">
@@ -17650,19 +17650,19 @@
         <v>583</v>
       </c>
       <c r="F248" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G248" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H248">
-        <v>0.33</v>
+        <v>0.08600000292062759</v>
       </c>
       <c r="I248">
-        <v>0.33</v>
+        <v>0.5230000019073486</v>
       </c>
       <c r="J248">
-        <v>0.34</v>
+        <v>0.3910000026226044</v>
       </c>
     </row>
     <row r="249" spans="1:10">
@@ -17682,19 +17682,19 @@
         <v>584</v>
       </c>
       <c r="F249" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G249" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H249">
-        <v>0.33</v>
+        <v>0.1669999957084656</v>
       </c>
       <c r="I249">
-        <v>0.33</v>
+        <v>0.4639999866485596</v>
       </c>
       <c r="J249">
-        <v>0.34</v>
+        <v>0.3689999878406525</v>
       </c>
     </row>
     <row r="250" spans="1:10">
@@ -17714,19 +17714,19 @@
         <v>583</v>
       </c>
       <c r="F250" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G250" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H250">
-        <v>0.33</v>
+        <v>0.1920000016689301</v>
       </c>
       <c r="I250">
-        <v>0.33</v>
+        <v>0.4790000021457672</v>
       </c>
       <c r="J250">
-        <v>0.34</v>
+        <v>0.3289999961853027</v>
       </c>
     </row>
     <row r="251" spans="1:10">
@@ -17746,19 +17746,19 @@
         <v>583</v>
       </c>
       <c r="F251" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G251" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H251">
-        <v>0.33</v>
+        <v>0.1120000034570694</v>
       </c>
       <c r="I251">
-        <v>0.33</v>
+        <v>0.593999981880188</v>
       </c>
       <c r="J251">
-        <v>0.34</v>
+        <v>0.2930000126361847</v>
       </c>
     </row>
     <row r="252" spans="1:10">
@@ -17778,19 +17778,19 @@
         <v>584</v>
       </c>
       <c r="F252" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G252" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H252">
-        <v>0.33</v>
+        <v>0.1019999980926514</v>
       </c>
       <c r="I252">
-        <v>0.33</v>
+        <v>0.4659999907016754</v>
       </c>
       <c r="J252">
-        <v>0.34</v>
+        <v>0.4320000112056732</v>
       </c>
     </row>
     <row r="253" spans="1:10">
@@ -17810,19 +17810,19 @@
         <v>583</v>
       </c>
       <c r="F253" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G253" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H253">
-        <v>0.33</v>
+        <v>0.1570000052452087</v>
       </c>
       <c r="I253">
-        <v>0.33</v>
+        <v>0.2230000048875809</v>
       </c>
       <c r="J253">
-        <v>0.34</v>
+        <v>0.6200000047683716</v>
       </c>
     </row>
     <row r="254" spans="1:10">
@@ -17842,19 +17842,19 @@
         <v>583</v>
       </c>
       <c r="F254" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G254" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H254">
-        <v>0.33</v>
+        <v>0.1080000028014183</v>
       </c>
       <c r="I254">
-        <v>0.33</v>
+        <v>0.4909999966621399</v>
       </c>
       <c r="J254">
-        <v>0.34</v>
+        <v>0.4000000059604645</v>
       </c>
     </row>
     <row r="255" spans="1:10">
@@ -17874,19 +17874,19 @@
         <v>584</v>
       </c>
       <c r="F255" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G255" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H255">
-        <v>0.33</v>
+        <v>0.08699999749660492</v>
       </c>
       <c r="I255">
-        <v>0.33</v>
+        <v>0.3540000021457672</v>
       </c>
       <c r="J255">
-        <v>0.34</v>
+        <v>0.5590000152587891</v>
       </c>
     </row>
     <row r="256" spans="1:10">
@@ -17906,19 +17906,19 @@
         <v>583</v>
       </c>
       <c r="F256" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G256" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H256">
-        <v>0.33</v>
+        <v>0.07100000232458115</v>
       </c>
       <c r="I256">
-        <v>0.33</v>
+        <v>0.6909999847412109</v>
       </c>
       <c r="J256">
-        <v>0.34</v>
+        <v>0.2380000054836273</v>
       </c>
     </row>
     <row r="257" spans="1:10">
@@ -17938,19 +17938,19 @@
         <v>583</v>
       </c>
       <c r="F257" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G257" t="s">
         <v>584</v>
       </c>
       <c r="H257">
-        <v>0.33</v>
+        <v>0.1319999992847443</v>
       </c>
       <c r="I257">
-        <v>0.33</v>
+        <v>0.3840000033378601</v>
       </c>
       <c r="J257">
-        <v>0.34</v>
+        <v>0.4839999973773956</v>
       </c>
     </row>
     <row r="258" spans="1:10">
@@ -17970,19 +17970,19 @@
         <v>583</v>
       </c>
       <c r="F258" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G258" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H258">
-        <v>0.33</v>
+        <v>0.1070000007748604</v>
       </c>
       <c r="I258">
-        <v>0.33</v>
+        <v>0.1749999970197678</v>
       </c>
       <c r="J258">
-        <v>0.34</v>
+        <v>0.7179999947547913</v>
       </c>
     </row>
     <row r="259" spans="1:10">
@@ -18002,19 +18002,19 @@
         <v>583</v>
       </c>
       <c r="F259" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G259" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H259">
-        <v>0.33</v>
+        <v>0.08799999952316284</v>
       </c>
       <c r="I259">
-        <v>0.33</v>
+        <v>0.4169999957084656</v>
       </c>
       <c r="J259">
-        <v>0.34</v>
+        <v>0.4959999918937683</v>
       </c>
     </row>
     <row r="260" spans="1:10">
@@ -18034,19 +18034,19 @@
         <v>584</v>
       </c>
       <c r="F260" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G260" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H260">
-        <v>0.33</v>
+        <v>0.07599999755620956</v>
       </c>
       <c r="I260">
-        <v>0.33</v>
+        <v>0.6420000195503235</v>
       </c>
       <c r="J260">
-        <v>0.34</v>
+        <v>0.2820000052452087</v>
       </c>
     </row>
     <row r="261" spans="1:10">
@@ -18066,19 +18066,19 @@
         <v>584</v>
       </c>
       <c r="F261" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G261" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H261">
-        <v>0.33</v>
+        <v>0.1369999945163727</v>
       </c>
       <c r="I261">
-        <v>0.33</v>
+        <v>0.4230000078678131</v>
       </c>
       <c r="J261">
-        <v>0.34</v>
+        <v>0.4399999976158142</v>
       </c>
     </row>
     <row r="262" spans="1:10">
@@ -18098,19 +18098,19 @@
         <v>583</v>
       </c>
       <c r="F262" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G262" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H262">
-        <v>0.33</v>
+        <v>0.1770000010728836</v>
       </c>
       <c r="I262">
-        <v>0.33</v>
+        <v>0.2119999974966049</v>
       </c>
       <c r="J262">
-        <v>0.34</v>
+        <v>0.6110000014305115</v>
       </c>
     </row>
     <row r="263" spans="1:10">
@@ -18136,13 +18136,13 @@
         <v>584</v>
       </c>
       <c r="H263">
-        <v>0.33</v>
+        <v>0.4569999873638153</v>
       </c>
       <c r="I263">
-        <v>0.33</v>
+        <v>0.1710000038146973</v>
       </c>
       <c r="J263">
-        <v>0.34</v>
+        <v>0.3720000088214874</v>
       </c>
     </row>
     <row r="264" spans="1:10">
@@ -18162,19 +18162,19 @@
         <v>583</v>
       </c>
       <c r="F264" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G264" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H264">
-        <v>0.33</v>
+        <v>0.153999999165535</v>
       </c>
       <c r="I264">
-        <v>0.33</v>
+        <v>0.5450000166893005</v>
       </c>
       <c r="J264">
-        <v>0.34</v>
+        <v>0.3009999990463257</v>
       </c>
     </row>
     <row r="265" spans="1:10">
@@ -18194,19 +18194,19 @@
         <v>584</v>
       </c>
       <c r="F265" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G265" t="s">
         <v>584</v>
       </c>
       <c r="H265">
-        <v>0.33</v>
+        <v>0.0689999982714653</v>
       </c>
       <c r="I265">
-        <v>0.33</v>
+        <v>0.6890000104904175</v>
       </c>
       <c r="J265">
-        <v>0.34</v>
+        <v>0.2409999966621399</v>
       </c>
     </row>
     <row r="266" spans="1:10">
@@ -18226,19 +18226,19 @@
         <v>584</v>
       </c>
       <c r="F266" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G266" t="s">
         <v>584</v>
       </c>
       <c r="H266">
-        <v>0.33</v>
+        <v>0.1529999971389771</v>
       </c>
       <c r="I266">
-        <v>0.33</v>
+        <v>0.210999995470047</v>
       </c>
       <c r="J266">
-        <v>0.34</v>
+        <v>0.6349999904632568</v>
       </c>
     </row>
     <row r="267" spans="1:10">
@@ -18258,19 +18258,19 @@
         <v>583</v>
       </c>
       <c r="F267" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G267" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H267">
-        <v>0.33</v>
+        <v>0.1289999932050705</v>
       </c>
       <c r="I267">
-        <v>0.33</v>
+        <v>0.2380000054836273</v>
       </c>
       <c r="J267">
-        <v>0.34</v>
+        <v>0.6330000162124634</v>
       </c>
     </row>
     <row r="268" spans="1:10">
@@ -18290,19 +18290,19 @@
         <v>584</v>
       </c>
       <c r="F268" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G268" t="s">
         <v>584</v>
       </c>
       <c r="H268">
-        <v>0.33</v>
+        <v>0.1059999987483025</v>
       </c>
       <c r="I268">
-        <v>0.33</v>
+        <v>0.5410000085830688</v>
       </c>
       <c r="J268">
-        <v>0.34</v>
+        <v>0.3529999852180481</v>
       </c>
     </row>
     <row r="269" spans="1:10">
@@ -18322,19 +18322,19 @@
         <v>583</v>
       </c>
       <c r="F269" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G269" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H269">
-        <v>0.33</v>
+        <v>0.2070000022649765</v>
       </c>
       <c r="I269">
-        <v>0.33</v>
+        <v>0.5419999957084656</v>
       </c>
       <c r="J269">
-        <v>0.34</v>
+        <v>0.2509999871253967</v>
       </c>
     </row>
     <row r="270" spans="1:10">
@@ -18354,19 +18354,19 @@
         <v>583</v>
       </c>
       <c r="F270" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G270" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H270">
-        <v>0.33</v>
+        <v>0.1159999966621399</v>
       </c>
       <c r="I270">
-        <v>0.33</v>
+        <v>0.4239999949932098</v>
       </c>
       <c r="J270">
-        <v>0.34</v>
+        <v>0.4600000083446503</v>
       </c>
     </row>
     <row r="271" spans="1:10">
@@ -18386,19 +18386,19 @@
         <v>584</v>
       </c>
       <c r="F271" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G271" t="s">
         <v>584</v>
       </c>
       <c r="H271">
-        <v>0.33</v>
+        <v>0.1589999943971634</v>
       </c>
       <c r="I271">
-        <v>0.33</v>
+        <v>0.4620000123977661</v>
       </c>
       <c r="J271">
-        <v>0.34</v>
+        <v>0.3790000081062317</v>
       </c>
     </row>
     <row r="272" spans="1:10">
@@ -18418,19 +18418,19 @@
         <v>583</v>
       </c>
       <c r="F272" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G272" t="s">
         <v>584</v>
       </c>
       <c r="H272">
-        <v>0.33</v>
+        <v>0.1220000013709068</v>
       </c>
       <c r="I272">
-        <v>0.33</v>
+        <v>0.3810000121593475</v>
       </c>
       <c r="J272">
-        <v>0.34</v>
+        <v>0.4970000088214874</v>
       </c>
     </row>
     <row r="273" spans="1:10">
@@ -18450,19 +18450,19 @@
         <v>583</v>
       </c>
       <c r="F273" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G273" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H273">
-        <v>0.33</v>
+        <v>0.164000004529953</v>
       </c>
       <c r="I273">
-        <v>0.33</v>
+        <v>0.5979999899864197</v>
       </c>
       <c r="J273">
-        <v>0.34</v>
+        <v>0.2380000054836273</v>
       </c>
     </row>
     <row r="274" spans="1:10">
@@ -18479,19 +18479,19 @@
         <v>584</v>
       </c>
       <c r="F274" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G274" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H274">
-        <v>0.33</v>
+        <v>0.09799999743700027</v>
       </c>
       <c r="I274">
-        <v>0.33</v>
+        <v>0.4560000002384186</v>
       </c>
       <c r="J274">
-        <v>0.34</v>
+        <v>0.4460000097751617</v>
       </c>
     </row>
     <row r="275" spans="1:10">
@@ -18511,19 +18511,19 @@
         <v>584</v>
       </c>
       <c r="F275" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G275" t="s">
         <v>584</v>
       </c>
       <c r="H275">
-        <v>0.33</v>
+        <v>0.1150000020861626</v>
       </c>
       <c r="I275">
-        <v>0.33</v>
+        <v>0.2689999938011169</v>
       </c>
       <c r="J275">
-        <v>0.34</v>
+        <v>0.6150000095367432</v>
       </c>
     </row>
     <row r="276" spans="1:10">
@@ -18543,19 +18543,19 @@
         <v>583</v>
       </c>
       <c r="F276" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G276" t="s">
         <v>584</v>
       </c>
       <c r="H276">
-        <v>0.33</v>
+        <v>0.1720000058412552</v>
       </c>
       <c r="I276">
-        <v>0.33</v>
+        <v>0.4289999902248383</v>
       </c>
       <c r="J276">
-        <v>0.34</v>
+        <v>0.3989999890327454</v>
       </c>
     </row>
     <row r="277" spans="1:10">
@@ -18575,19 +18575,19 @@
         <v>583</v>
       </c>
       <c r="F277" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G277" t="s">
         <v>584</v>
       </c>
       <c r="H277">
-        <v>0.33</v>
+        <v>0.1369999945163727</v>
       </c>
       <c r="I277">
-        <v>0.33</v>
+        <v>0.4029999971389771</v>
       </c>
       <c r="J277">
-        <v>0.34</v>
+        <v>0.4600000083446503</v>
       </c>
     </row>
     <row r="278" spans="1:10">
@@ -18607,19 +18607,19 @@
         <v>583</v>
       </c>
       <c r="F278" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G278" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H278">
-        <v>0.33</v>
+        <v>0.1710000038146973</v>
       </c>
       <c r="I278">
-        <v>0.33</v>
+        <v>0.5770000219345093</v>
       </c>
       <c r="J278">
-        <v>0.34</v>
+        <v>0.2520000040531158</v>
       </c>
     </row>
     <row r="279" spans="1:10">
@@ -18636,19 +18636,19 @@
         <v>584</v>
       </c>
       <c r="F279" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G279" t="s">
         <v>584</v>
       </c>
       <c r="H279">
-        <v>0.33</v>
+        <v>0.1459999978542328</v>
       </c>
       <c r="I279">
-        <v>0.33</v>
+        <v>0.5899999737739563</v>
       </c>
       <c r="J279">
-        <v>0.34</v>
+        <v>0.2630000114440918</v>
       </c>
     </row>
     <row r="280" spans="1:10">
@@ -18668,19 +18668,19 @@
         <v>583</v>
       </c>
       <c r="F280" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G280" t="s">
         <v>584</v>
       </c>
       <c r="H280">
-        <v>0.33</v>
+        <v>0.1689999997615814</v>
       </c>
       <c r="I280">
-        <v>0.33</v>
+        <v>0.3269999921321869</v>
       </c>
       <c r="J280">
-        <v>0.34</v>
+        <v>0.5040000081062317</v>
       </c>
     </row>
     <row r="281" spans="1:10">
@@ -18700,19 +18700,19 @@
         <v>583</v>
       </c>
       <c r="F281" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G281" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H281">
-        <v>0.33</v>
+        <v>0.1650000065565109</v>
       </c>
       <c r="I281">
-        <v>0.33</v>
+        <v>0.3199999928474426</v>
       </c>
       <c r="J281">
-        <v>0.34</v>
+        <v>0.5149999856948853</v>
       </c>
     </row>
     <row r="282" spans="1:10">
@@ -18732,19 +18732,19 @@
         <v>583</v>
       </c>
       <c r="F282" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G282" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H282">
-        <v>0.33</v>
+        <v>0.1019999980926514</v>
       </c>
       <c r="I282">
-        <v>0.33</v>
+        <v>0.3889999985694885</v>
       </c>
       <c r="J282">
-        <v>0.34</v>
+        <v>0.5090000033378601</v>
       </c>
     </row>
     <row r="283" spans="1:10">
@@ -18764,19 +18764,19 @@
         <v>584</v>
       </c>
       <c r="F283" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G283" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H283">
-        <v>0.33</v>
+        <v>0.1260000020265579</v>
       </c>
       <c r="I283">
-        <v>0.33</v>
+        <v>0.5580000281333923</v>
       </c>
       <c r="J283">
-        <v>0.34</v>
+        <v>0.3160000145435333</v>
       </c>
     </row>
     <row r="284" spans="1:10">
@@ -18796,19 +18796,19 @@
         <v>583</v>
       </c>
       <c r="F284" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G284" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H284">
-        <v>0.33</v>
+        <v>0.1780000030994415</v>
       </c>
       <c r="I284">
-        <v>0.33</v>
+        <v>0.3260000050067902</v>
       </c>
       <c r="J284">
-        <v>0.34</v>
+        <v>0.4959999918937683</v>
       </c>
     </row>
     <row r="285" spans="1:10">
@@ -18828,19 +18828,19 @@
         <v>584</v>
       </c>
       <c r="F285" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G285" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H285">
-        <v>0.33</v>
+        <v>0.08399999886751175</v>
       </c>
       <c r="I285">
-        <v>0.33</v>
+        <v>0.2949999868869781</v>
       </c>
       <c r="J285">
-        <v>0.34</v>
+        <v>0.6209999918937683</v>
       </c>
     </row>
     <row r="286" spans="1:10">
@@ -18860,19 +18860,19 @@
         <v>584</v>
       </c>
       <c r="F286" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G286" t="s">
         <v>584</v>
       </c>
       <c r="H286">
-        <v>0.33</v>
+        <v>0.1379999965429306</v>
       </c>
       <c r="I286">
-        <v>0.33</v>
+        <v>0.6449999809265137</v>
       </c>
       <c r="J286">
-        <v>0.34</v>
+        <v>0.2179999947547913</v>
       </c>
     </row>
     <row r="287" spans="1:10">
@@ -18892,19 +18892,19 @@
         <v>583</v>
       </c>
       <c r="F287" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G287" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H287">
-        <v>0.33</v>
+        <v>0.07800000160932541</v>
       </c>
       <c r="I287">
-        <v>0.33</v>
+        <v>0.6420000195503235</v>
       </c>
       <c r="J287">
-        <v>0.34</v>
+        <v>0.2800000011920929</v>
       </c>
     </row>
     <row r="288" spans="1:10">
@@ -18924,19 +18924,19 @@
         <v>583</v>
       </c>
       <c r="F288" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G288" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H288">
-        <v>0.33</v>
+        <v>0.08299999684095383</v>
       </c>
       <c r="I288">
-        <v>0.33</v>
+        <v>0.6380000114440918</v>
       </c>
       <c r="J288">
-        <v>0.34</v>
+        <v>0.2790000140666962</v>
       </c>
     </row>
     <row r="289" spans="1:10">
@@ -18956,19 +18956,19 @@
         <v>584</v>
       </c>
       <c r="F289" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G289" t="s">
         <v>584</v>
       </c>
       <c r="H289">
-        <v>0.33</v>
+        <v>0.1500000059604645</v>
       </c>
       <c r="I289">
-        <v>0.33</v>
+        <v>0.3889999985694885</v>
       </c>
       <c r="J289">
-        <v>0.34</v>
+        <v>0.4620000123977661</v>
       </c>
     </row>
     <row r="290" spans="1:10">
@@ -18988,19 +18988,19 @@
         <v>584</v>
       </c>
       <c r="F290" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G290" t="s">
         <v>584</v>
       </c>
       <c r="H290">
-        <v>0.33</v>
+        <v>0.1850000023841858</v>
       </c>
       <c r="I290">
-        <v>0.33</v>
+        <v>0.4749999940395355</v>
       </c>
       <c r="J290">
-        <v>0.34</v>
+        <v>0.3400000035762787</v>
       </c>
     </row>
     <row r="291" spans="1:10">
@@ -19020,19 +19020,19 @@
         <v>583</v>
       </c>
       <c r="F291" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G291" t="s">
         <v>584</v>
       </c>
       <c r="H291">
-        <v>0.33</v>
+        <v>0.07400000095367432</v>
       </c>
       <c r="I291">
-        <v>0.33</v>
+        <v>0.5360000133514404</v>
       </c>
       <c r="J291">
-        <v>0.34</v>
+        <v>0.3889999985694885</v>
       </c>
     </row>
     <row r="292" spans="1:10">
@@ -19052,19 +19052,19 @@
         <v>583</v>
       </c>
       <c r="F292" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G292" t="s">
         <v>584</v>
       </c>
       <c r="H292">
-        <v>0.33</v>
+        <v>0.1500000059604645</v>
       </c>
       <c r="I292">
-        <v>0.33</v>
+        <v>0.5289999842643738</v>
       </c>
       <c r="J292">
-        <v>0.34</v>
+        <v>0.3210000097751617</v>
       </c>
     </row>
     <row r="293" spans="1:10">
@@ -19084,19 +19084,19 @@
         <v>583</v>
       </c>
       <c r="F293" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G293" t="s">
         <v>584</v>
       </c>
       <c r="H293">
-        <v>0.33</v>
+        <v>0.1059999987483025</v>
       </c>
       <c r="I293">
-        <v>0.33</v>
+        <v>0.453000009059906</v>
       </c>
       <c r="J293">
-        <v>0.34</v>
+        <v>0.4399999976158142</v>
       </c>
     </row>
     <row r="294" spans="1:10">
@@ -19116,19 +19116,19 @@
         <v>584</v>
       </c>
       <c r="F294" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G294" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H294">
-        <v>0.33</v>
+        <v>0.1560000032186508</v>
       </c>
       <c r="I294">
-        <v>0.33</v>
+        <v>0.5090000033378601</v>
       </c>
       <c r="J294">
-        <v>0.34</v>
+        <v>0.3350000083446503</v>
       </c>
     </row>
     <row r="295" spans="1:10">
@@ -19148,19 +19148,19 @@
         <v>584</v>
       </c>
       <c r="F295" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G295" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H295">
-        <v>0.33</v>
+        <v>0.07199999690055847</v>
       </c>
       <c r="I295">
-        <v>0.33</v>
+        <v>0.6470000147819519</v>
       </c>
       <c r="J295">
-        <v>0.34</v>
+        <v>0.2809999883174896</v>
       </c>
     </row>
   </sheetData>
